--- a/FEBRUARY 2026/FLOOR FEBRUARY 2026.xlsx
+++ b/FEBRUARY 2026/FLOOR FEBRUARY 2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="15980" windowHeight="17020" firstSheet="2" activeTab="2"/>
+    <workbookView windowWidth="11260" windowHeight="17020" firstSheet="3" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Anugrah (Bag, Cup, Box)" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="50">
   <si>
     <t>DATE</t>
   </si>
@@ -92,6 +92,15 @@
     <t>GRAND TOTAL</t>
   </si>
   <si>
+    <t>0925/JL/UTM/0226</t>
+  </si>
+  <si>
+    <t>THINWALL CUP 60 ML 50 PCS</t>
+  </si>
+  <si>
+    <t>MIRCOFIBER CLOTH</t>
+  </si>
+  <si>
     <t>0967/JL/UTM/0226</t>
   </si>
   <si>
@@ -101,6 +110,30 @@
     <t>PIPING BAG</t>
   </si>
   <si>
+    <t>1290/JL/UTM/0226</t>
+  </si>
+  <si>
+    <t>FLAME GUN</t>
+  </si>
+  <si>
+    <t>1366/JL/UTM/0226</t>
+  </si>
+  <si>
+    <t>CUP INJECTION 400 ML + LID 25 PCS</t>
+  </si>
+  <si>
+    <t>PAPER CUP BROWN 12 OZ 50 PCS</t>
+  </si>
+  <si>
+    <t>LID CUP 12/16 OZ HOT 50 PCS</t>
+  </si>
+  <si>
+    <t>1419/JL/UTM/0226</t>
+  </si>
+  <si>
+    <t>TISSUE COCKTAIL NAPKIN PLENTY 100SX48</t>
+  </si>
+  <si>
     <t>SO05LC2602000202/00</t>
   </si>
   <si>
@@ -126,6 +159,9 @@
   </si>
   <si>
     <t>DISHY 5 L DISHWASHIG</t>
+  </si>
+  <si>
+    <t>DETERGENT 5 L</t>
   </si>
   <si>
     <t>NO</t>
@@ -163,10 +199,10 @@
     <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="180" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="181" formatCode="[$-409]d\-mmm\-yyyy;@"/>
-    <numFmt numFmtId="182" formatCode="dd\-mmm"/>
-    <numFmt numFmtId="183" formatCode="_ [$IDR]\ * #,##0_ ;_ [$IDR]\ * \-#,##0_ ;_ [$IDR]\ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="184" formatCode="[$Rp-421]#,##0.0000;[Red][$Rp-421]#,##0.0000"/>
-    <numFmt numFmtId="185" formatCode="[$Rp-421]#,##0.00;[Red][$Rp-421]#,##0.00"/>
+    <numFmt numFmtId="182" formatCode="[$Rp-421]#,##0.00;[Red][$Rp-421]#,##0.00"/>
+    <numFmt numFmtId="183" formatCode="dd\-mmm"/>
+    <numFmt numFmtId="184" formatCode="_ [$IDR]\ * #,##0_ ;_ [$IDR]\ * \-#,##0_ ;_ [$IDR]\ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="185" formatCode="[$Rp-421]#,##0.0000;[Red][$Rp-421]#,##0.0000"/>
   </numFmts>
   <fonts count="33">
     <font>
@@ -680,7 +716,9 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -703,8 +741,32 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -722,16 +784,14 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -743,30 +803,6 @@
       </right>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1037,7 +1073,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="169">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1072,6 +1108,12 @@
     <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="181" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1090,49 +1132,67 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="181" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="181" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="3" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="3" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="3" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="2" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1147,7 +1207,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1156,22 +1216,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="184" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1189,16 +1249,16 @@
     <xf numFmtId="181" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1207,7 +1267,7 @@
     <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1216,28 +1276,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1246,127 +1306,204 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="184" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="185" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="185" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="185" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="185" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="184" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="185" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="185" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="185" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="184" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="180" fontId="8" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="185" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="8" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="185" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="182" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="9" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="181" fontId="9" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="9" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="181" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="181" fontId="9" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="9" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="9" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="9" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="9" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="182" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="9" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="9" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="9" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1375,23 +1512,35 @@
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="9" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="180" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1552,13 +1701,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>26035</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>48260</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>4774565</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>1617980</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1576,8 +1725,160 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm rot="16200000">
-          <a:off x="8837930" y="-512445"/>
+          <a:off x="8837930" y="2789555"/>
           <a:ext cx="3220720" cy="4748530"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>49847</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>27622</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>4743767</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>2619057</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="ID_E8302BE2CFDC4A71BEBC26BFA38F5A58" descr="PHOTO-2026-02-13-18-36-40"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="9148445" y="5782945"/>
+          <a:ext cx="2591435" cy="4693920"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>35560</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>27940</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>4757420</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>871220</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="ID_606766B8363C4E56B1FDD9ABD6689511" descr="PHOTO-2026-02-17-14-54-26"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="9133840" y="8437880"/>
+          <a:ext cx="2621280" cy="4721860"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>33020</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>27940</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>4759960</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>2665730</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="ID_C430EFB4A259471A99F44531A92C7D1B" descr="PHOTO-2026-02-17-14-54-46"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="9125585" y="11110595"/>
+          <a:ext cx="2637790" cy="4726940"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>30797</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>27622</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>4762182</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>1637982</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="ID_4CF906F51B7D4C548EBD747200265355" descr="PHOTO-2026-02-07-21-45-07"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="8813165" y="-504190"/>
+          <a:ext cx="3261360" cy="4730750"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1666,6 +1967,45 @@
         <a:xfrm rot="16200000">
           <a:off x="7288530" y="-299085"/>
           <a:ext cx="3693795" cy="5245735"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>31750</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>73025</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>5321935</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>1835150</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="ID_F931166EF4414168B791978EC6974601" descr="PHOTO-2026-02-17-12-59-25"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:srcRect l="7896" t="14529" r="17782" b="4338"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="7301865" y="3470910"/>
+          <a:ext cx="3667125" cy="5290185"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1938,256 +2278,256 @@
   <dimension ref="A1:H12"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20.4" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="17.4296875" style="94"/>
-    <col min="2" max="2" width="13.4296875" style="94" customWidth="1"/>
-    <col min="3" max="3" width="36" style="94" customWidth="1"/>
-    <col min="4" max="4" width="21.2890625" style="93" customWidth="1"/>
-    <col min="5" max="5" width="33.2890625" style="94" customWidth="1"/>
-    <col min="6" max="6" width="17.2890625" style="94" customWidth="1"/>
-    <col min="7" max="8" width="20.859375" style="94" customWidth="1"/>
-    <col min="9" max="9" width="12.859375" style="94"/>
-    <col min="10" max="10" width="15" style="94"/>
-    <col min="11" max="16384" width="18.0390625" style="94"/>
+    <col min="1" max="1" width="17.4296875" style="104"/>
+    <col min="2" max="2" width="13.4296875" style="104" customWidth="1"/>
+    <col min="3" max="3" width="36" style="104" customWidth="1"/>
+    <col min="4" max="4" width="21.2890625" style="103" customWidth="1"/>
+    <col min="5" max="5" width="33.2890625" style="104" customWidth="1"/>
+    <col min="6" max="6" width="17.2890625" style="104" customWidth="1"/>
+    <col min="7" max="8" width="20.859375" style="104" customWidth="1"/>
+    <col min="9" max="9" width="12.859375" style="104"/>
+    <col min="10" max="10" width="15" style="104"/>
+    <col min="11" max="16384" width="18.0390625" style="104"/>
   </cols>
   <sheetData>
-    <row r="1" s="92" customFormat="1" ht="16" customHeight="1" spans="1:8">
-      <c r="A1" s="119" t="s">
+    <row r="1" s="100" customFormat="1" ht="16" customHeight="1" spans="1:8">
+      <c r="A1" s="154" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="120" t="s">
+      <c r="B1" s="155" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="120" t="s">
+      <c r="C1" s="155" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="120" t="s">
+      <c r="D1" s="155" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="120" t="s">
+      <c r="E1" s="155" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="120" t="s">
+      <c r="F1" s="155" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="120" t="s">
+      <c r="G1" s="155" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="120" t="s">
+      <c r="H1" s="155" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" s="92" customFormat="1" ht="140" customHeight="1" spans="1:8">
-      <c r="A2" s="97">
+    <row r="2" s="100" customFormat="1" ht="140" customHeight="1" spans="1:8">
+      <c r="A2" s="114">
         <v>46056</v>
       </c>
-      <c r="B2" s="107">
+      <c r="B2" s="156">
         <v>3426</v>
       </c>
-      <c r="C2" s="121" t="s">
+      <c r="C2" s="157" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="122">
+      <c r="D2" s="158">
         <v>20</v>
       </c>
-      <c r="E2" s="109"/>
-      <c r="F2" s="110">
+      <c r="E2" s="139"/>
+      <c r="F2" s="161">
         <v>55000</v>
       </c>
-      <c r="G2" s="112">
+      <c r="G2" s="162">
         <f>SUM(D2*F2)</f>
         <v>1100000</v>
       </c>
-      <c r="H2" s="112">
+      <c r="H2" s="162">
         <f>SUM(G2:G3)</f>
         <v>1650000</v>
       </c>
     </row>
-    <row r="3" s="92" customFormat="1" ht="140" customHeight="1" spans="1:8">
-      <c r="A3" s="103"/>
-      <c r="B3" s="107"/>
-      <c r="C3" s="121" t="s">
+    <row r="3" s="100" customFormat="1" ht="140" customHeight="1" spans="1:8">
+      <c r="A3" s="117"/>
+      <c r="B3" s="156"/>
+      <c r="C3" s="157" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="122">
+      <c r="D3" s="158">
         <v>10</v>
       </c>
-      <c r="E3" s="113"/>
-      <c r="F3" s="110">
+      <c r="E3" s="143"/>
+      <c r="F3" s="161">
         <v>55000</v>
       </c>
-      <c r="G3" s="112">
+      <c r="G3" s="162">
         <f>SUM(D3*F3)</f>
         <v>550000</v>
       </c>
-      <c r="H3" s="114"/>
-    </row>
-    <row r="4" s="92" customFormat="1" ht="40" customHeight="1" spans="1:8">
-      <c r="A4" s="97">
+      <c r="H3" s="163"/>
+    </row>
+    <row r="4" s="100" customFormat="1" ht="40" customHeight="1" spans="1:8">
+      <c r="A4" s="114">
         <v>46058</v>
       </c>
-      <c r="B4" s="98">
+      <c r="B4" s="115">
         <v>3461</v>
       </c>
-      <c r="C4" s="102" t="s">
+      <c r="C4" s="123" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="122">
+      <c r="D4" s="158">
         <v>450</v>
       </c>
-      <c r="E4" s="109"/>
-      <c r="F4" s="112">
+      <c r="E4" s="139"/>
+      <c r="F4" s="162">
         <v>1800</v>
       </c>
-      <c r="G4" s="112">
+      <c r="G4" s="162">
         <f>SUM(D4*F4)</f>
         <v>810000</v>
       </c>
-      <c r="H4" s="112">
+      <c r="H4" s="162">
         <f>SUM(G4:G10)</f>
         <v>1641500</v>
       </c>
     </row>
-    <row r="5" s="92" customFormat="1" ht="40" customHeight="1" spans="1:8">
-      <c r="A5" s="103"/>
-      <c r="B5" s="104"/>
-      <c r="C5" s="107" t="s">
+    <row r="5" s="100" customFormat="1" ht="40" customHeight="1" spans="1:8">
+      <c r="A5" s="117"/>
+      <c r="B5" s="118"/>
+      <c r="C5" s="156" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="107">
+      <c r="D5" s="156">
         <v>100</v>
       </c>
-      <c r="E5" s="113"/>
-      <c r="F5" s="126">
+      <c r="E5" s="143"/>
+      <c r="F5" s="164">
         <v>630</v>
       </c>
-      <c r="G5" s="112">
+      <c r="G5" s="162">
         <f>SUM(D5*F5)</f>
         <v>63000</v>
       </c>
-      <c r="H5" s="114"/>
-    </row>
-    <row r="6" s="92" customFormat="1" ht="40" customHeight="1" spans="1:8">
-      <c r="A6" s="103"/>
-      <c r="B6" s="104"/>
-      <c r="C6" s="107" t="s">
+      <c r="H5" s="163"/>
+    </row>
+    <row r="6" s="100" customFormat="1" ht="40" customHeight="1" spans="1:8">
+      <c r="A6" s="117"/>
+      <c r="B6" s="118"/>
+      <c r="C6" s="156" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="107">
+      <c r="D6" s="156">
         <v>36</v>
       </c>
-      <c r="E6" s="113"/>
-      <c r="F6" s="126">
+      <c r="E6" s="143"/>
+      <c r="F6" s="164">
         <f>G6/D6</f>
         <v>3166.66666666667</v>
       </c>
-      <c r="G6" s="112">
+      <c r="G6" s="162">
         <v>114000</v>
       </c>
-      <c r="H6" s="114"/>
-    </row>
-    <row r="7" s="92" customFormat="1" ht="40" customHeight="1" spans="1:8">
-      <c r="A7" s="103"/>
-      <c r="B7" s="104"/>
-      <c r="C7" s="98" t="s">
+      <c r="H6" s="163"/>
+    </row>
+    <row r="7" s="100" customFormat="1" ht="40" customHeight="1" spans="1:8">
+      <c r="A7" s="117"/>
+      <c r="B7" s="118"/>
+      <c r="C7" s="115" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="123">
+      <c r="D7" s="115">
         <v>36</v>
       </c>
-      <c r="E7" s="113"/>
-      <c r="F7" s="126">
+      <c r="E7" s="143"/>
+      <c r="F7" s="164">
         <f>G7/D7</f>
         <v>2666.66666666667</v>
       </c>
-      <c r="G7" s="112">
+      <c r="G7" s="162">
         <v>96000</v>
       </c>
-      <c r="H7" s="114"/>
-    </row>
-    <row r="8" s="92" customFormat="1" ht="40" customHeight="1" spans="1:8">
-      <c r="A8" s="103"/>
-      <c r="B8" s="104"/>
-      <c r="C8" s="123" t="s">
+      <c r="H7" s="163"/>
+    </row>
+    <row r="8" s="100" customFormat="1" ht="40" customHeight="1" spans="1:8">
+      <c r="A8" s="117"/>
+      <c r="B8" s="118"/>
+      <c r="C8" s="115" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="123">
+      <c r="D8" s="115">
         <v>10</v>
       </c>
-      <c r="E8" s="113"/>
-      <c r="F8" s="126">
+      <c r="E8" s="143"/>
+      <c r="F8" s="164">
         <v>23000</v>
       </c>
-      <c r="G8" s="112">
+      <c r="G8" s="162">
         <f>F8*D8</f>
         <v>230000</v>
       </c>
-      <c r="H8" s="114"/>
-    </row>
-    <row r="9" s="92" customFormat="1" ht="40" customHeight="1" spans="1:8">
-      <c r="A9" s="103"/>
-      <c r="B9" s="104"/>
-      <c r="C9" s="123" t="s">
+      <c r="H8" s="163"/>
+    </row>
+    <row r="9" s="100" customFormat="1" ht="40" customHeight="1" spans="1:8">
+      <c r="A9" s="117"/>
+      <c r="B9" s="118"/>
+      <c r="C9" s="115" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="123">
+      <c r="D9" s="115">
         <v>7</v>
       </c>
-      <c r="E9" s="113"/>
-      <c r="F9" s="126">
+      <c r="E9" s="143"/>
+      <c r="F9" s="164">
         <f>G9/D9</f>
         <v>38000</v>
       </c>
-      <c r="G9" s="112">
+      <c r="G9" s="162">
         <v>266000</v>
       </c>
-      <c r="H9" s="114"/>
-    </row>
-    <row r="10" s="92" customFormat="1" ht="40" customHeight="1" spans="1:8">
-      <c r="A10" s="103"/>
-      <c r="B10" s="104"/>
-      <c r="C10" s="98" t="s">
+      <c r="H9" s="163"/>
+    </row>
+    <row r="10" s="100" customFormat="1" ht="40" customHeight="1" spans="1:8">
+      <c r="A10" s="117"/>
+      <c r="B10" s="118"/>
+      <c r="C10" s="115" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="98">
+      <c r="D10" s="115">
         <v>5</v>
       </c>
-      <c r="E10" s="113"/>
-      <c r="F10" s="126">
+      <c r="E10" s="143"/>
+      <c r="F10" s="164">
         <f>G10/D10</f>
         <v>12500</v>
       </c>
-      <c r="G10" s="112">
+      <c r="G10" s="162">
         <v>62500</v>
       </c>
-      <c r="H10" s="114"/>
-    </row>
-    <row r="11" s="92" customFormat="1" ht="258" customHeight="1" spans="1:8">
-      <c r="A11" s="106"/>
-      <c r="B11" s="107"/>
-      <c r="C11" s="107"/>
-      <c r="D11" s="107"/>
-      <c r="E11" s="117"/>
-      <c r="F11" s="127"/>
-      <c r="G11" s="110">
+      <c r="H10" s="163"/>
+    </row>
+    <row r="11" s="100" customFormat="1" ht="258" customHeight="1" spans="1:8">
+      <c r="A11" s="121"/>
+      <c r="B11" s="156"/>
+      <c r="C11" s="156"/>
+      <c r="D11" s="156"/>
+      <c r="E11" s="165"/>
+      <c r="F11" s="166"/>
+      <c r="G11" s="161">
         <f>SUM(D11*F11)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="110">
+      <c r="H11" s="161">
         <f>SUM(G11)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" s="92" customFormat="1" ht="18" customHeight="1" spans="1:8">
-      <c r="A12" s="124" t="s">
+    <row r="12" s="100" customFormat="1" ht="18" customHeight="1" spans="1:8">
+      <c r="A12" s="159" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="125"/>
-      <c r="C12" s="125"/>
-      <c r="D12" s="125"/>
-      <c r="E12" s="125"/>
-      <c r="F12" s="125"/>
-      <c r="G12" s="128"/>
-      <c r="H12" s="129">
+      <c r="B12" s="160"/>
+      <c r="C12" s="160"/>
+      <c r="D12" s="160"/>
+      <c r="E12" s="160"/>
+      <c r="F12" s="160"/>
+      <c r="G12" s="167"/>
+      <c r="H12" s="168">
         <f>SUM(H2:H11)</f>
         <v>3291500</v>
       </c>
@@ -2213,167 +2553,321 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20.4" outlineLevelRow="7" outlineLevelCol="7"/>
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20.4" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="19.859375" style="93"/>
-    <col min="2" max="2" width="21.6875" style="93" customWidth="1"/>
-    <col min="3" max="3" width="43.0390625" style="93" customWidth="1"/>
-    <col min="4" max="4" width="14.4296875" style="93" customWidth="1"/>
-    <col min="5" max="5" width="58.9609375" style="94" customWidth="1"/>
-    <col min="6" max="6" width="19.5234375" style="94" customWidth="1"/>
-    <col min="7" max="8" width="20.859375" style="94" customWidth="1"/>
-    <col min="9" max="9" width="12.859375" style="94"/>
-    <col min="10" max="16384" width="9.140625" style="94"/>
+    <col min="1" max="1" width="19.859375" style="103"/>
+    <col min="2" max="2" width="21.6875" style="103" customWidth="1"/>
+    <col min="3" max="3" width="43.0390625" style="103" customWidth="1"/>
+    <col min="4" max="4" width="14.4296875" style="103" customWidth="1"/>
+    <col min="5" max="5" width="58.9609375" style="104" customWidth="1"/>
+    <col min="6" max="6" width="19.5234375" style="105" customWidth="1"/>
+    <col min="7" max="7" width="20.859375" style="105" customWidth="1"/>
+    <col min="8" max="8" width="20.859375" style="106" customWidth="1"/>
+    <col min="9" max="9" width="12.859375" style="104"/>
+    <col min="10" max="16384" width="9.140625" style="104"/>
   </cols>
   <sheetData>
-    <row r="1" s="92" customFormat="1" ht="16" customHeight="1" spans="1:8">
-      <c r="A1" s="95" t="s">
+    <row r="1" s="100" customFormat="1" ht="16" customHeight="1" spans="1:8">
+      <c r="A1" s="107" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="108" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="96" t="s">
+      <c r="C1" s="108" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="96" t="s">
+      <c r="D1" s="108" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="96" t="s">
+      <c r="E1" s="108" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="96" t="s">
+      <c r="F1" s="134" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="96" t="s">
+      <c r="G1" s="134" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="96" t="s">
+      <c r="H1" s="135" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" s="92" customFormat="1" ht="130" customHeight="1" spans="1:8">
-      <c r="A2" s="97">
+    <row r="2" s="100" customFormat="1" ht="130" customHeight="1" spans="1:8">
+      <c r="A2" s="109">
+        <v>46055</v>
+      </c>
+      <c r="B2" s="110" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="111" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="20">
+        <v>2</v>
+      </c>
+      <c r="E2" s="110"/>
+      <c r="F2" s="136">
+        <v>360000</v>
+      </c>
+      <c r="G2" s="136">
+        <f>D2*F2</f>
+        <v>720000</v>
+      </c>
+      <c r="H2" s="137">
+        <f>SUM(G2:G3)</f>
+        <v>870000</v>
+      </c>
+    </row>
+    <row r="3" s="100" customFormat="1" ht="130" customHeight="1" spans="1:8">
+      <c r="A3" s="112"/>
+      <c r="B3" s="113"/>
+      <c r="C3" s="111" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="20">
+        <v>6</v>
+      </c>
+      <c r="E3" s="113"/>
+      <c r="F3" s="136">
+        <v>25000</v>
+      </c>
+      <c r="G3" s="136">
+        <f>D3*F3</f>
+        <v>150000</v>
+      </c>
+      <c r="H3" s="138"/>
+    </row>
+    <row r="4" s="100" customFormat="1" ht="130" customHeight="1" spans="1:8">
+      <c r="A4" s="114">
         <v>46056</v>
       </c>
-      <c r="B2" s="98" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="99" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="99">
+      <c r="B4" s="115" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="116" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="116">
         <v>3</v>
       </c>
-      <c r="E2" s="109"/>
-      <c r="F2" s="110">
+      <c r="E4" s="139"/>
+      <c r="F4" s="140">
         <v>45000</v>
       </c>
-      <c r="G2" s="111">
-        <f>D2*F2</f>
+      <c r="G4" s="141">
+        <f>D4*F4</f>
         <v>135000</v>
       </c>
-      <c r="H2" s="112">
-        <f>SUM(G2:G3)</f>
+      <c r="H4" s="142">
+        <f>SUM(G4:G5)</f>
         <v>515000</v>
       </c>
     </row>
-    <row r="3" s="92" customFormat="1" ht="130" customHeight="1" spans="1:8">
-      <c r="A3" s="100"/>
-      <c r="B3" s="101"/>
-      <c r="C3" s="102" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="99">
+    <row r="5" s="100" customFormat="1" ht="130" customHeight="1" spans="1:8">
+      <c r="A5" s="117"/>
+      <c r="B5" s="118"/>
+      <c r="C5" s="119" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="120">
         <v>10</v>
       </c>
-      <c r="E3" s="113"/>
-      <c r="F3" s="111">
+      <c r="E5" s="143"/>
+      <c r="F5" s="142">
         <v>38000</v>
       </c>
-      <c r="G3" s="111">
-        <f>D3*F3</f>
+      <c r="G5" s="142">
+        <f>D5*F5</f>
         <v>380000</v>
       </c>
-      <c r="H3" s="114"/>
-    </row>
-    <row r="4" s="92" customFormat="1" ht="83" customHeight="1" spans="1:8">
-      <c r="A4" s="97"/>
-      <c r="B4" s="98"/>
-      <c r="C4" s="102"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111">
-        <f>D4*F4</f>
-        <v>0</v>
-      </c>
-      <c r="H4" s="112">
-        <f>SUM(G4:G6)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" s="92" customFormat="1" ht="83" customHeight="1" spans="1:8">
-      <c r="A5" s="103"/>
-      <c r="B5" s="104"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="105"/>
-      <c r="E5" s="113"/>
-      <c r="F5" s="112"/>
-      <c r="G5" s="111">
-        <f>D5*F5</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="114"/>
-    </row>
-    <row r="6" s="92" customFormat="1" ht="83" customHeight="1" spans="1:8">
-      <c r="A6" s="100"/>
-      <c r="B6" s="101"/>
-      <c r="C6" s="102"/>
-      <c r="D6" s="105"/>
-      <c r="E6" s="115"/>
-      <c r="F6" s="112"/>
-      <c r="G6" s="111">
+      <c r="H5" s="144"/>
+    </row>
+    <row r="6" s="101" customFormat="1" ht="208.9" customHeight="1" spans="1:8">
+      <c r="A6" s="121">
+        <v>46066</v>
+      </c>
+      <c r="B6" s="122" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="123" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="116">
+        <v>3</v>
+      </c>
+      <c r="E6" s="145"/>
+      <c r="F6" s="141">
+        <v>75000</v>
+      </c>
+      <c r="G6" s="141">
         <f>D6*F6</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="116"/>
-    </row>
-    <row r="7" s="92" customFormat="1" ht="200" customHeight="1" spans="1:8">
-      <c r="A7" s="106"/>
-      <c r="B7" s="107"/>
-      <c r="C7" s="102"/>
-      <c r="D7" s="105"/>
-      <c r="E7" s="117"/>
-      <c r="F7" s="112"/>
-      <c r="G7" s="112"/>
-      <c r="H7" s="110"/>
-    </row>
-    <row r="8" s="92" customFormat="1" spans="1:8">
-      <c r="A8" s="108"/>
-      <c r="B8" s="108"/>
-      <c r="C8" s="108"/>
-      <c r="D8" s="108"/>
-      <c r="E8" s="108"/>
-      <c r="F8" s="108"/>
-      <c r="G8" s="118"/>
-      <c r="H8" s="118">
-        <f>SUM(H2:H7)</f>
-        <v>515000</v>
+        <v>225000</v>
+      </c>
+      <c r="H6" s="141">
+        <f>SUM(G6)</f>
+        <v>225000</v>
+      </c>
+    </row>
+    <row r="7" s="101" customFormat="1" ht="70" customHeight="1" spans="1:8">
+      <c r="A7" s="124">
+        <v>46069</v>
+      </c>
+      <c r="B7" s="125" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="123" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="116">
+        <v>40</v>
+      </c>
+      <c r="E7" s="146"/>
+      <c r="F7" s="141">
+        <v>35000</v>
+      </c>
+      <c r="G7" s="141">
+        <f>F7*D7</f>
+        <v>1400000</v>
+      </c>
+      <c r="H7" s="147">
+        <f>SUM(G7:G9)</f>
+        <v>5920000</v>
+      </c>
+    </row>
+    <row r="8" s="101" customFormat="1" ht="70" customHeight="1" spans="1:8">
+      <c r="A8" s="124"/>
+      <c r="B8" s="125"/>
+      <c r="C8" s="123" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="116">
+        <v>40</v>
+      </c>
+      <c r="E8" s="146"/>
+      <c r="F8" s="141">
+        <v>75000</v>
+      </c>
+      <c r="G8" s="141">
+        <f>F8*D8</f>
+        <v>3000000</v>
+      </c>
+      <c r="H8" s="147"/>
+    </row>
+    <row r="9" s="102" customFormat="1" ht="70" customHeight="1" spans="1:8">
+      <c r="A9" s="124"/>
+      <c r="B9" s="125"/>
+      <c r="C9" s="123" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="116">
+        <v>40</v>
+      </c>
+      <c r="E9" s="146"/>
+      <c r="F9" s="141">
+        <v>38000</v>
+      </c>
+      <c r="G9" s="141">
+        <f>F9*D9</f>
+        <v>1520000</v>
+      </c>
+      <c r="H9" s="147"/>
+    </row>
+    <row r="10" s="100" customFormat="1" ht="211.1" customHeight="1" spans="1:8">
+      <c r="A10" s="126">
+        <v>46070</v>
+      </c>
+      <c r="B10" s="127" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="128" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="129">
+        <v>2</v>
+      </c>
+      <c r="E10" s="148"/>
+      <c r="F10" s="149">
+        <v>295000</v>
+      </c>
+      <c r="G10" s="149">
+        <f>F10*D10</f>
+        <v>590000</v>
+      </c>
+      <c r="H10" s="150">
+        <f>SUM(G10)</f>
+        <v>590000</v>
+      </c>
+    </row>
+    <row r="11" s="100" customFormat="1" spans="1:8">
+      <c r="A11" s="126"/>
+      <c r="B11" s="127"/>
+      <c r="C11" s="128"/>
+      <c r="D11" s="116"/>
+      <c r="E11" s="148"/>
+      <c r="F11" s="141"/>
+      <c r="G11" s="141"/>
+      <c r="H11" s="150"/>
+    </row>
+    <row r="12" s="100" customFormat="1" spans="1:8">
+      <c r="A12" s="126"/>
+      <c r="B12" s="127"/>
+      <c r="C12" s="128"/>
+      <c r="D12" s="116"/>
+      <c r="E12" s="148"/>
+      <c r="F12" s="141"/>
+      <c r="G12" s="141"/>
+      <c r="H12" s="150"/>
+    </row>
+    <row r="13" s="100" customFormat="1" spans="1:8">
+      <c r="A13" s="126"/>
+      <c r="B13" s="127"/>
+      <c r="C13" s="128"/>
+      <c r="D13" s="116"/>
+      <c r="E13" s="148"/>
+      <c r="F13" s="141"/>
+      <c r="G13" s="141"/>
+      <c r="H13" s="150"/>
+    </row>
+    <row r="14" s="100" customFormat="1" spans="1:8">
+      <c r="A14" s="130"/>
+      <c r="B14" s="131"/>
+      <c r="C14" s="132"/>
+      <c r="D14" s="116"/>
+      <c r="E14" s="151"/>
+      <c r="F14" s="140"/>
+      <c r="G14" s="141"/>
+      <c r="H14" s="149"/>
+    </row>
+    <row r="15" s="100" customFormat="1" spans="1:8">
+      <c r="A15" s="133"/>
+      <c r="B15" s="133"/>
+      <c r="C15" s="133"/>
+      <c r="D15" s="133"/>
+      <c r="E15" s="133"/>
+      <c r="F15" s="152"/>
+      <c r="G15" s="153"/>
+      <c r="H15" s="153">
+        <f>SUM(H2:H14)</f>
+        <v>8120000</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A8:E8"/>
+  <mergeCells count="13">
+    <mergeCell ref="A15:E15"/>
     <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
     <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B7:B9"/>
     <mergeCell ref="E2:E3"/>
-    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="E7:E9"/>
     <mergeCell ref="H2:H3"/>
-    <mergeCell ref="H4:H6"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="H7:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -2398,201 +2892,201 @@
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1" spans="1:7">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="51" t="s">
+      <c r="C1" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="51" t="s">
+      <c r="D1" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="51" t="s">
+      <c r="E1" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="51" t="s">
+      <c r="F1" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="51" t="s">
+      <c r="G1" s="59" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" ht="123.5" customHeight="1" spans="1:7">
-      <c r="A2" s="52">
+      <c r="A2" s="60">
         <v>46055</v>
       </c>
-      <c r="B2" s="39" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="54">
+      <c r="B2" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="61" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="62">
         <v>80</v>
       </c>
-      <c r="E2" s="73"/>
-      <c r="F2" s="74">
+      <c r="E2" s="81"/>
+      <c r="F2" s="82">
         <v>6063.9632</v>
       </c>
-      <c r="G2" s="75">
+      <c r="G2" s="83">
         <f>SUM(D2*F2)</f>
         <v>485117.056</v>
       </c>
     </row>
     <row r="3" ht="191" customHeight="1" spans="1:7">
-      <c r="A3" s="52"/>
-      <c r="B3" s="39"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="75"/>
+      <c r="A3" s="60"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="84"/>
+      <c r="G3" s="83"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="52"/>
-      <c r="B4" s="57" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="57"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="78">
+      <c r="A4" s="60"/>
+      <c r="B4" s="65" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="65"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="86">
         <f>SUM(G2:G3)</f>
         <v>485117.056</v>
       </c>
-      <c r="I4" s="91"/>
+      <c r="I4" s="99"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="52"/>
-      <c r="B5" s="57" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="57"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="78">
+      <c r="A5" s="60"/>
+      <c r="B5" s="65" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="65"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="85"/>
+      <c r="G5" s="86">
         <f>G4*11%</f>
         <v>53362.87616</v>
       </c>
-      <c r="I5" s="91"/>
+      <c r="I5" s="99"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="52"/>
-      <c r="B6" s="57" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="57"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="78">
+      <c r="A6" s="60"/>
+      <c r="B6" s="65" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="65"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="85"/>
+      <c r="G6" s="86">
         <f>((G4*100)/111)*0.111%</f>
         <v>485.117056</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="52"/>
-      <c r="B7" s="57" t="s">
+      <c r="A7" s="60"/>
+      <c r="B7" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="57"/>
-      <c r="D7" s="58"/>
-      <c r="E7" s="79"/>
-      <c r="F7" s="80"/>
-      <c r="G7" s="81">
+      <c r="C7" s="65"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="87"/>
+      <c r="F7" s="88"/>
+      <c r="G7" s="89">
         <f>SUM(G4:G6)</f>
         <v>538965.049216</v>
       </c>
     </row>
     <row r="8" ht="123.5" customHeight="1" spans="1:7">
-      <c r="A8" s="52"/>
-      <c r="B8" s="59"/>
-      <c r="C8" s="60"/>
-      <c r="D8" s="61"/>
-      <c r="E8" s="82"/>
-      <c r="F8" s="83"/>
-      <c r="G8" s="84"/>
+      <c r="A8" s="60"/>
+      <c r="B8" s="67"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="90"/>
+      <c r="F8" s="91"/>
+      <c r="G8" s="92"/>
     </row>
     <row r="9" ht="123.5" customHeight="1" spans="1:7">
-      <c r="A9" s="52"/>
-      <c r="B9" s="62"/>
-      <c r="C9" s="60"/>
-      <c r="D9" s="61"/>
-      <c r="E9" s="85"/>
-      <c r="F9" s="83"/>
-      <c r="G9" s="84"/>
+      <c r="A9" s="60"/>
+      <c r="B9" s="70"/>
+      <c r="C9" s="68"/>
+      <c r="D9" s="69"/>
+      <c r="E9" s="93"/>
+      <c r="F9" s="91"/>
+      <c r="G9" s="92"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="63"/>
-      <c r="B10" s="57" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="57"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="86"/>
-      <c r="F10" s="77"/>
-      <c r="G10" s="78">
+      <c r="A10" s="71"/>
+      <c r="B10" s="65" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="65"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="94"/>
+      <c r="F10" s="85"/>
+      <c r="G10" s="86">
         <f>SUM(G8:G9)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="64"/>
-      <c r="B11" s="65" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="66"/>
-      <c r="D11" s="58"/>
-      <c r="E11" s="86"/>
-      <c r="F11" s="77"/>
-      <c r="G11" s="78"/>
+      <c r="A11" s="72"/>
+      <c r="B11" s="73" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="74"/>
+      <c r="D11" s="66"/>
+      <c r="E11" s="94"/>
+      <c r="F11" s="85"/>
+      <c r="G11" s="86"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="63"/>
-      <c r="B12" s="57" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="57"/>
-      <c r="D12" s="58"/>
-      <c r="E12" s="86"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="78">
+      <c r="A12" s="71"/>
+      <c r="B12" s="65" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="65"/>
+      <c r="D12" s="66"/>
+      <c r="E12" s="94"/>
+      <c r="F12" s="85"/>
+      <c r="G12" s="86">
         <f>((G10*100)/111)*0.111%</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="67"/>
-      <c r="B13" s="68" t="s">
+      <c r="A13" s="75"/>
+      <c r="B13" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="69"/>
-      <c r="D13" s="58"/>
-      <c r="E13" s="79"/>
-      <c r="F13" s="87"/>
-      <c r="G13" s="81">
+      <c r="C13" s="77"/>
+      <c r="D13" s="66"/>
+      <c r="E13" s="87"/>
+      <c r="F13" s="95"/>
+      <c r="G13" s="89">
         <f>SUM(G10:G12)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="70" t="s">
+      <c r="A14" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="71"/>
-      <c r="C14" s="71"/>
-      <c r="D14" s="72"/>
-      <c r="E14" s="88">
+      <c r="B14" s="79"/>
+      <c r="C14" s="79"/>
+      <c r="D14" s="80"/>
+      <c r="E14" s="96">
         <f>G7+G13</f>
         <v>538965.049216</v>
       </c>
-      <c r="F14" s="89"/>
-      <c r="G14" s="90"/>
+      <c r="F14" s="97"/>
+      <c r="G14" s="98"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -2630,253 +3124,253 @@
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="10.5703125" style="12" customWidth="1"/>
-    <col min="2" max="2" width="12.6015625" style="36" customWidth="1"/>
+    <col min="2" max="2" width="12.6015625" style="44" customWidth="1"/>
     <col min="3" max="3" width="36.125" style="12" customWidth="1"/>
     <col min="4" max="4" width="18.828125" style="12" customWidth="1"/>
     <col min="5" max="5" width="12.2890625" style="12" customWidth="1"/>
     <col min="6" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" s="35" customFormat="1" ht="19" customHeight="1" spans="1:5">
-      <c r="A1" s="37" t="s">
+    <row r="1" s="43" customFormat="1" ht="19" customHeight="1" spans="1:5">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="37" t="s">
+      <c r="C1" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="37" t="s">
-        <v>26</v>
+      <c r="E1" s="45" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="2" s="12" customFormat="1" ht="263.65" customHeight="1" spans="1:5">
-      <c r="A2" s="39"/>
-      <c r="B2" s="40"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="41"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="49"/>
     </row>
     <row r="3" s="12" customFormat="1" ht="255.1" customHeight="1" spans="1:5">
-      <c r="A3" s="39"/>
-      <c r="B3" s="40"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="48"/>
+      <c r="A3" s="47"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="56"/>
     </row>
     <row r="4" s="12" customFormat="1" ht="249.95" customHeight="1" spans="1:5">
-      <c r="A4" s="39"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="48"/>
+      <c r="A4" s="47"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="56"/>
     </row>
     <row r="5" s="12" customFormat="1" ht="256.25" customHeight="1" spans="1:5">
-      <c r="A5" s="39"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="48"/>
+      <c r="A5" s="47"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="56"/>
     </row>
     <row r="6" s="12" customFormat="1" ht="253.85" customHeight="1" spans="1:5">
-      <c r="A6" s="39"/>
-      <c r="B6" s="40"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="48"/>
+      <c r="A6" s="47"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="56"/>
     </row>
     <row r="7" s="12" customFormat="1" ht="254.65" customHeight="1" spans="1:5">
-      <c r="A7" s="39"/>
-      <c r="B7" s="40"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="43"/>
-      <c r="E7" s="48"/>
+      <c r="A7" s="47"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="56"/>
     </row>
     <row r="8" s="12" customFormat="1" ht="255.35" customHeight="1" spans="1:5">
-      <c r="A8" s="39"/>
-      <c r="B8" s="40"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="48"/>
+      <c r="A8" s="47"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="56"/>
     </row>
     <row r="9" s="12" customFormat="1" ht="266.95" customHeight="1" spans="1:5">
-      <c r="A9" s="39"/>
-      <c r="B9" s="40"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="48"/>
+      <c r="A9" s="47"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="56"/>
     </row>
     <row r="10" s="12" customFormat="1" ht="261.95" customHeight="1" spans="1:5">
-      <c r="A10" s="39"/>
-      <c r="B10" s="40"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="43"/>
-      <c r="E10" s="48"/>
+      <c r="A10" s="47"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="49"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="56"/>
     </row>
     <row r="11" s="12" customFormat="1" ht="261.9" customHeight="1" spans="1:5">
-      <c r="A11" s="39"/>
-      <c r="B11" s="40"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="48"/>
+      <c r="A11" s="47"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="56"/>
     </row>
     <row r="12" s="12" customFormat="1" ht="270.7" customHeight="1" spans="1:5">
-      <c r="A12" s="39"/>
-      <c r="B12" s="40"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="43"/>
-      <c r="E12" s="48"/>
+      <c r="A12" s="47"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="56"/>
     </row>
     <row r="13" s="12" customFormat="1" ht="261.1" customHeight="1" spans="1:5">
-      <c r="A13" s="39"/>
-      <c r="B13" s="40"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="48"/>
+      <c r="A13" s="47"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="56"/>
     </row>
     <row r="14" s="12" customFormat="1" ht="257.15" customHeight="1" spans="1:5">
-      <c r="A14" s="39"/>
-      <c r="B14" s="40"/>
-      <c r="C14" s="41"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="48"/>
+      <c r="A14" s="47"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="56"/>
     </row>
     <row r="15" s="12" customFormat="1" ht="263.55" customHeight="1" spans="1:5">
-      <c r="A15" s="39"/>
-      <c r="B15" s="40"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="48"/>
+      <c r="A15" s="47"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="56"/>
     </row>
     <row r="16" s="12" customFormat="1" ht="270.35" customHeight="1" spans="1:5">
-      <c r="A16" s="39"/>
-      <c r="B16" s="40"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="48"/>
+      <c r="A16" s="47"/>
+      <c r="B16" s="48"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="56"/>
     </row>
     <row r="17" s="12" customFormat="1" ht="261.7" customHeight="1" spans="1:5">
-      <c r="A17" s="39"/>
-      <c r="B17" s="40"/>
-      <c r="C17" s="41"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="48"/>
+      <c r="A17" s="47"/>
+      <c r="B17" s="48"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="56"/>
     </row>
     <row r="18" s="12" customFormat="1" ht="260" customHeight="1" spans="1:5">
-      <c r="A18" s="39"/>
-      <c r="B18" s="40"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="48"/>
+      <c r="A18" s="47"/>
+      <c r="B18" s="48"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="56"/>
     </row>
     <row r="19" s="12" customFormat="1" ht="263.2" customHeight="1" spans="1:5">
-      <c r="A19" s="39"/>
-      <c r="B19" s="40"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="43"/>
-      <c r="E19" s="48"/>
+      <c r="A19" s="47"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="56"/>
     </row>
     <row r="20" s="12" customFormat="1" ht="289.95" customHeight="1" spans="1:5">
-      <c r="A20" s="39"/>
-      <c r="B20" s="40"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="43"/>
-      <c r="E20" s="48"/>
+      <c r="A20" s="47"/>
+      <c r="B20" s="48"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="56"/>
     </row>
     <row r="21" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A21" s="39"/>
-      <c r="B21" s="40"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="43"/>
-      <c r="E21" s="48"/>
+      <c r="A21" s="47"/>
+      <c r="B21" s="48"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="56"/>
     </row>
     <row r="22" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A22" s="39"/>
-      <c r="B22" s="40"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="48"/>
+      <c r="A22" s="47"/>
+      <c r="B22" s="48"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="56"/>
     </row>
     <row r="23" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A23" s="39"/>
-      <c r="B23" s="40"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="43"/>
-      <c r="E23" s="48"/>
+      <c r="A23" s="47"/>
+      <c r="B23" s="48"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="56"/>
     </row>
     <row r="24" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A24" s="39"/>
-      <c r="B24" s="40"/>
-      <c r="C24" s="41"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="41"/>
+      <c r="A24" s="47"/>
+      <c r="B24" s="48"/>
+      <c r="C24" s="49"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="49"/>
     </row>
     <row r="25" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A25" s="39"/>
-      <c r="B25" s="40"/>
-      <c r="C25" s="41"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="41"/>
+      <c r="A25" s="47"/>
+      <c r="B25" s="48"/>
+      <c r="C25" s="49"/>
+      <c r="D25" s="50"/>
+      <c r="E25" s="49"/>
     </row>
     <row r="26" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A26" s="39"/>
-      <c r="B26" s="40"/>
-      <c r="C26" s="41"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="41"/>
+      <c r="A26" s="47"/>
+      <c r="B26" s="48"/>
+      <c r="C26" s="49"/>
+      <c r="D26" s="50"/>
+      <c r="E26" s="49"/>
     </row>
     <row r="27" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A27" s="39">
+      <c r="A27" s="47">
         <v>45960</v>
       </c>
-      <c r="B27" s="40"/>
-      <c r="C27" s="41"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="41"/>
+      <c r="B27" s="48"/>
+      <c r="C27" s="49"/>
+      <c r="D27" s="50"/>
+      <c r="E27" s="49"/>
     </row>
     <row r="28" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A28" s="39">
+      <c r="A28" s="47">
         <v>45961</v>
       </c>
-      <c r="B28" s="40"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="42"/>
-      <c r="E28" s="41"/>
+      <c r="B28" s="48"/>
+      <c r="C28" s="49"/>
+      <c r="D28" s="50"/>
+      <c r="E28" s="49"/>
     </row>
     <row r="29" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A29" s="39"/>
-      <c r="B29" s="40"/>
-      <c r="C29" s="41"/>
-      <c r="D29" s="42"/>
-      <c r="E29" s="41"/>
+      <c r="A29" s="47"/>
+      <c r="B29" s="48"/>
+      <c r="C29" s="49"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="49"/>
     </row>
     <row r="30" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A30" s="39"/>
-      <c r="B30" s="40"/>
-      <c r="C30" s="41"/>
-      <c r="D30" s="42"/>
-      <c r="E30" s="41"/>
+      <c r="A30" s="47"/>
+      <c r="B30" s="48"/>
+      <c r="C30" s="49"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="49"/>
     </row>
     <row r="31" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A31" s="39"/>
-      <c r="B31" s="40"/>
-      <c r="C31" s="41"/>
-      <c r="D31" s="42"/>
-      <c r="E31" s="41"/>
+      <c r="A31" s="47"/>
+      <c r="B31" s="48"/>
+      <c r="C31" s="49"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="49"/>
     </row>
     <row r="32" s="12" customFormat="1" spans="1:5">
-      <c r="A32" s="44"/>
-      <c r="B32" s="45"/>
-      <c r="C32" s="46">
+      <c r="A32" s="52"/>
+      <c r="B32" s="53"/>
+      <c r="C32" s="54">
         <f>SUM(D2:D31)</f>
         <v>0</v>
       </c>
-      <c r="D32" s="47"/>
-      <c r="E32" s="49"/>
+      <c r="D32" s="55"/>
+      <c r="E32" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2896,113 +3390,136 @@
   <cols>
     <col min="1" max="1" width="21.140625" style="13" customWidth="1"/>
     <col min="2" max="2" width="27.5703125" style="12" customWidth="1"/>
-    <col min="3" max="3" width="30.75" style="12" customWidth="1"/>
+    <col min="3" max="3" width="30.75" style="14" customWidth="1"/>
     <col min="4" max="4" width="65.703125" style="12" customWidth="1"/>
-    <col min="5" max="7" width="32.3359375" style="12" customWidth="1"/>
+    <col min="5" max="7" width="32.3359375" style="15" customWidth="1"/>
     <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" s="11" customFormat="1" ht="35" customHeight="1" spans="1:7">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="D1" s="15" t="s">
+      <c r="B1" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="35" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" s="12" customFormat="1" ht="296.45" customHeight="1" spans="1:7">
-      <c r="A2" s="16">
+      <c r="A2" s="18">
         <v>46056</v>
       </c>
-      <c r="B2" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="18">
+      <c r="B2" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="20">
         <v>5</v>
       </c>
-      <c r="D2" s="19"/>
-      <c r="E2" s="25">
+      <c r="D2" s="21"/>
+      <c r="E2" s="36">
         <v>60000</v>
       </c>
-      <c r="F2" s="26">
+      <c r="F2" s="37">
         <f>C2*E2</f>
         <v>300000</v>
       </c>
-      <c r="G2" s="27">
+      <c r="G2" s="36">
         <f>SUM(F2:F2)</f>
         <v>300000</v>
       </c>
     </row>
-    <row r="3" s="12" customFormat="1" ht="80" customHeight="1" spans="1:7">
-      <c r="A3" s="20"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="30"/>
-    </row>
-    <row r="4" s="12" customFormat="1" ht="80" customHeight="1" spans="1:7">
-      <c r="A4" s="20"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="31"/>
+    <row r="3" s="12" customFormat="1" ht="150" customHeight="1" spans="1:7">
+      <c r="A3" s="22">
+        <v>46069</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="24">
+        <v>10</v>
+      </c>
+      <c r="D3" s="25"/>
+      <c r="E3" s="38">
+        <v>55000</v>
+      </c>
+      <c r="F3" s="37">
+        <f>C3*E3</f>
+        <v>550000</v>
+      </c>
+      <c r="G3" s="39">
+        <f>SUM(F3:F4)</f>
+        <v>825000</v>
+      </c>
+    </row>
+    <row r="4" s="12" customFormat="1" ht="150" customHeight="1" spans="1:7">
+      <c r="A4" s="26"/>
+      <c r="B4" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="24">
+        <v>5</v>
+      </c>
+      <c r="D4" s="28"/>
+      <c r="E4" s="38">
+        <v>55000</v>
+      </c>
+      <c r="F4" s="37">
+        <f>C4*E4</f>
+        <v>275000</v>
+      </c>
+      <c r="G4" s="40"/>
     </row>
     <row r="5" s="12" customFormat="1" ht="80" customHeight="1" spans="1:7">
-      <c r="A5" s="20"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="32"/>
+      <c r="A5" s="29"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="42"/>
     </row>
     <row r="6" s="12" customFormat="1" ht="26" spans="1:7">
-      <c r="A6" s="20"/>
-      <c r="B6" s="21"/>
-      <c r="C6" s="22"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="33"/>
+      <c r="A6" s="32"/>
+      <c r="B6" s="33"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="42"/>
     </row>
     <row r="7" s="12" customFormat="1" ht="39" customHeight="1" spans="1:7">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="24"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="34">
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="42">
         <f>SUM(G2:G6)</f>
-        <v>300000</v>
+        <v>1125000</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="G3:G5"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="G3:G4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -3023,13 +3540,13 @@
   <sheetData>
     <row r="1" ht="25" customHeight="1" spans="1:3">
       <c r="A1" s="3" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3037,7 +3554,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C2" s="8">
         <f>'Anugrah (Bag, Cup, Box)'!H12</f>
@@ -3049,11 +3566,11 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C3" s="8">
-        <f>'UD Abdi Jaya (Bag, Cup, Box)'!H8</f>
-        <v>515000</v>
+        <f>'UD Abdi Jaya (Bag, Cup, Box)'!H15</f>
+        <v>8120000</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3061,7 +3578,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C4" s="8">
         <f>'PT. SUPARMA JAYA TBK (Tissue)'!E14</f>
@@ -3073,7 +3590,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C5" s="9">
         <f>'Vickel Laundry'!C32</f>
@@ -3085,11 +3602,11 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C6" s="9">
         <f>'Dishy Soap'!G7</f>
-        <v>300000</v>
+        <v>1125000</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -3099,7 +3616,7 @@
       <c r="B7" s="7"/>
       <c r="C7" s="10">
         <f>SUM(C2:C5)</f>
-        <v>4345465.049216</v>
+        <v>11950465.049216</v>
       </c>
     </row>
   </sheetData>

--- a/FEBRUARY 2026/FLOOR FEBRUARY 2026.xlsx
+++ b/FEBRUARY 2026/FLOOR FEBRUARY 2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11260" windowHeight="17020" firstSheet="3" activeTab="4"/>
+    <workbookView windowWidth="16360" windowHeight="18640" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Anugrah (Bag, Cup, Box)" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="56">
   <si>
     <t>DATE</t>
   </si>
@@ -134,6 +134,21 @@
     <t>TISSUE COCKTAIL NAPKIN PLENTY 100SX48</t>
   </si>
   <si>
+    <t>1593/JL/UTM/0226</t>
+  </si>
+  <si>
+    <t>KILAT PLASTIC 40</t>
+  </si>
+  <si>
+    <t>BLACK PLASTIC TRASH BAG 50X60 100 PCS</t>
+  </si>
+  <si>
+    <t>PAPER BAG HANDLE M</t>
+  </si>
+  <si>
+    <t>HEMP ROPE</t>
+  </si>
+  <si>
     <t>SO05LC2602000202/00</t>
   </si>
   <si>
@@ -147,6 +162,9 @@
   </si>
   <si>
     <t>PPh 22</t>
+  </si>
+  <si>
+    <t>SO05LC2602002826/00</t>
   </si>
   <si>
     <t>STATUS</t>
@@ -795,20 +813,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
+      <left/>
       <right/>
       <top/>
       <bottom style="thin">
@@ -825,6 +830,17 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1073,7 +1089,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="169">
+  <cellXfs count="161">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1240,6 +1256,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1267,7 +1284,7 @@
     <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="183" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1276,24 +1293,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1303,6 +1314,9 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1310,7 +1324,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="185" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1318,23 +1332,11 @@
     <xf numFmtId="185" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="185" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="185" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1346,9 +1348,7 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1356,12 +1356,10 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="182" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="182" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
@@ -1393,134 +1391,131 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="9" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="9" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="9" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="9" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="9" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="9" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="9" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="9" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="9" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="9" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1533,14 +1528,11 @@
     <xf numFmtId="184" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="184" fontId="9" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="184" fontId="9" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1887,6 +1879,44 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>27305</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>72390</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>4766945</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>641350</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="ID_2CD0977337A74D4BB3C4A73AD81BD252" descr="PHOTO-2026-02-25-21-16-41"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8075295" y="14880590"/>
+          <a:ext cx="4739640" cy="2664460"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1923,6 +1953,45 @@
         <a:xfrm>
           <a:off x="6073140" y="226060"/>
           <a:ext cx="2711450" cy="3960495"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>23495</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2805430</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>4034155</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="ID_41D803318DAD49E7860597AB1912F478" descr="PHOTO-2026-02-21-10-02-52"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:srcRect b="22446"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6037580" y="5073650"/>
+          <a:ext cx="2781935" cy="4011295"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2278,256 +2347,256 @@
   <dimension ref="A1:H12"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20.4" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="17.4296875" style="104"/>
-    <col min="2" max="2" width="13.4296875" style="104" customWidth="1"/>
-    <col min="3" max="3" width="36" style="104" customWidth="1"/>
-    <col min="4" max="4" width="21.2890625" style="103" customWidth="1"/>
-    <col min="5" max="5" width="33.2890625" style="104" customWidth="1"/>
-    <col min="6" max="6" width="17.2890625" style="104" customWidth="1"/>
-    <col min="7" max="8" width="20.859375" style="104" customWidth="1"/>
-    <col min="9" max="9" width="12.859375" style="104"/>
-    <col min="10" max="10" width="15" style="104"/>
-    <col min="11" max="16384" width="18.0390625" style="104"/>
+    <col min="1" max="1" width="17.4296875" style="98"/>
+    <col min="2" max="2" width="13.4296875" style="98" customWidth="1"/>
+    <col min="3" max="3" width="36" style="98" customWidth="1"/>
+    <col min="4" max="4" width="21.2890625" style="96" customWidth="1"/>
+    <col min="5" max="5" width="33.2890625" style="98" customWidth="1"/>
+    <col min="6" max="6" width="17.2890625" style="98" customWidth="1"/>
+    <col min="7" max="8" width="20.859375" style="98" customWidth="1"/>
+    <col min="9" max="9" width="12.859375" style="98"/>
+    <col min="10" max="10" width="15" style="98"/>
+    <col min="11" max="16384" width="18.0390625" style="98"/>
   </cols>
   <sheetData>
-    <row r="1" s="100" customFormat="1" ht="16" customHeight="1" spans="1:8">
-      <c r="A1" s="154" t="s">
+    <row r="1" s="94" customFormat="1" ht="16" customHeight="1" spans="1:8">
+      <c r="A1" s="147" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="155" t="s">
+      <c r="B1" s="148" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="155" t="s">
+      <c r="C1" s="148" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="155" t="s">
+      <c r="D1" s="148" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="155" t="s">
+      <c r="E1" s="148" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="155" t="s">
+      <c r="F1" s="148" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="155" t="s">
+      <c r="G1" s="148" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="155" t="s">
+      <c r="H1" s="148" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" s="100" customFormat="1" ht="140" customHeight="1" spans="1:8">
-      <c r="A2" s="114">
+    <row r="2" s="94" customFormat="1" ht="140" customHeight="1" spans="1:8">
+      <c r="A2" s="108">
         <v>46056</v>
       </c>
-      <c r="B2" s="156">
+      <c r="B2" s="119">
         <v>3426</v>
       </c>
-      <c r="C2" s="157" t="s">
+      <c r="C2" s="149" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="158">
+      <c r="D2" s="150">
         <v>20</v>
       </c>
-      <c r="E2" s="139"/>
-      <c r="F2" s="161">
+      <c r="E2" s="132"/>
+      <c r="F2" s="154">
         <v>55000</v>
       </c>
-      <c r="G2" s="162">
+      <c r="G2" s="155">
         <f>SUM(D2*F2)</f>
         <v>1100000</v>
       </c>
-      <c r="H2" s="162">
+      <c r="H2" s="155">
         <f>SUM(G2:G3)</f>
         <v>1650000</v>
       </c>
     </row>
-    <row r="3" s="100" customFormat="1" ht="140" customHeight="1" spans="1:8">
-      <c r="A3" s="117"/>
-      <c r="B3" s="156"/>
-      <c r="C3" s="157" t="s">
+    <row r="3" s="94" customFormat="1" ht="140" customHeight="1" spans="1:8">
+      <c r="A3" s="112"/>
+      <c r="B3" s="119"/>
+      <c r="C3" s="149" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="158">
+      <c r="D3" s="150">
         <v>10</v>
       </c>
-      <c r="E3" s="143"/>
-      <c r="F3" s="161">
+      <c r="E3" s="136"/>
+      <c r="F3" s="154">
         <v>55000</v>
       </c>
-      <c r="G3" s="162">
+      <c r="G3" s="155">
         <f>SUM(D3*F3)</f>
         <v>550000</v>
       </c>
-      <c r="H3" s="163"/>
-    </row>
-    <row r="4" s="100" customFormat="1" ht="40" customHeight="1" spans="1:8">
-      <c r="A4" s="114">
+      <c r="H3" s="156"/>
+    </row>
+    <row r="4" s="94" customFormat="1" ht="40" customHeight="1" spans="1:8">
+      <c r="A4" s="108">
         <v>46058</v>
       </c>
-      <c r="B4" s="115">
+      <c r="B4" s="109">
         <v>3461</v>
       </c>
-      <c r="C4" s="123" t="s">
+      <c r="C4" s="151" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="158">
+      <c r="D4" s="150">
         <v>450</v>
       </c>
-      <c r="E4" s="139"/>
-      <c r="F4" s="162">
+      <c r="E4" s="132"/>
+      <c r="F4" s="155">
         <v>1800</v>
       </c>
-      <c r="G4" s="162">
+      <c r="G4" s="155">
         <f>SUM(D4*F4)</f>
         <v>810000</v>
       </c>
-      <c r="H4" s="162">
+      <c r="H4" s="155">
         <f>SUM(G4:G10)</f>
         <v>1641500</v>
       </c>
     </row>
-    <row r="5" s="100" customFormat="1" ht="40" customHeight="1" spans="1:8">
-      <c r="A5" s="117"/>
-      <c r="B5" s="118"/>
-      <c r="C5" s="156" t="s">
+    <row r="5" s="94" customFormat="1" ht="40" customHeight="1" spans="1:8">
+      <c r="A5" s="112"/>
+      <c r="B5" s="113"/>
+      <c r="C5" s="119" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="156">
+      <c r="D5" s="119">
         <v>100</v>
       </c>
-      <c r="E5" s="143"/>
-      <c r="F5" s="164">
+      <c r="E5" s="136"/>
+      <c r="F5" s="157">
         <v>630</v>
       </c>
-      <c r="G5" s="162">
+      <c r="G5" s="155">
         <f>SUM(D5*F5)</f>
         <v>63000</v>
       </c>
-      <c r="H5" s="163"/>
-    </row>
-    <row r="6" s="100" customFormat="1" ht="40" customHeight="1" spans="1:8">
-      <c r="A6" s="117"/>
-      <c r="B6" s="118"/>
-      <c r="C6" s="156" t="s">
+      <c r="H5" s="156"/>
+    </row>
+    <row r="6" s="94" customFormat="1" ht="40" customHeight="1" spans="1:8">
+      <c r="A6" s="112"/>
+      <c r="B6" s="113"/>
+      <c r="C6" s="119" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="156">
+      <c r="D6" s="119">
         <v>36</v>
       </c>
-      <c r="E6" s="143"/>
-      <c r="F6" s="164">
+      <c r="E6" s="136"/>
+      <c r="F6" s="157">
         <f>G6/D6</f>
         <v>3166.66666666667</v>
       </c>
-      <c r="G6" s="162">
+      <c r="G6" s="155">
         <v>114000</v>
       </c>
-      <c r="H6" s="163"/>
-    </row>
-    <row r="7" s="100" customFormat="1" ht="40" customHeight="1" spans="1:8">
-      <c r="A7" s="117"/>
-      <c r="B7" s="118"/>
-      <c r="C7" s="115" t="s">
+      <c r="H6" s="156"/>
+    </row>
+    <row r="7" s="94" customFormat="1" ht="40" customHeight="1" spans="1:8">
+      <c r="A7" s="112"/>
+      <c r="B7" s="113"/>
+      <c r="C7" s="109" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="115">
+      <c r="D7" s="109">
         <v>36</v>
       </c>
-      <c r="E7" s="143"/>
-      <c r="F7" s="164">
+      <c r="E7" s="136"/>
+      <c r="F7" s="157">
         <f>G7/D7</f>
         <v>2666.66666666667</v>
       </c>
-      <c r="G7" s="162">
+      <c r="G7" s="155">
         <v>96000</v>
       </c>
-      <c r="H7" s="163"/>
-    </row>
-    <row r="8" s="100" customFormat="1" ht="40" customHeight="1" spans="1:8">
-      <c r="A8" s="117"/>
-      <c r="B8" s="118"/>
-      <c r="C8" s="115" t="s">
+      <c r="H7" s="156"/>
+    </row>
+    <row r="8" s="94" customFormat="1" ht="40" customHeight="1" spans="1:8">
+      <c r="A8" s="112"/>
+      <c r="B8" s="113"/>
+      <c r="C8" s="109" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="115">
+      <c r="D8" s="109">
         <v>10</v>
       </c>
-      <c r="E8" s="143"/>
-      <c r="F8" s="164">
+      <c r="E8" s="136"/>
+      <c r="F8" s="157">
         <v>23000</v>
       </c>
-      <c r="G8" s="162">
+      <c r="G8" s="155">
         <f>F8*D8</f>
         <v>230000</v>
       </c>
-      <c r="H8" s="163"/>
-    </row>
-    <row r="9" s="100" customFormat="1" ht="40" customHeight="1" spans="1:8">
-      <c r="A9" s="117"/>
-      <c r="B9" s="118"/>
-      <c r="C9" s="115" t="s">
+      <c r="H8" s="156"/>
+    </row>
+    <row r="9" s="94" customFormat="1" ht="40" customHeight="1" spans="1:8">
+      <c r="A9" s="112"/>
+      <c r="B9" s="113"/>
+      <c r="C9" s="109" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="115">
+      <c r="D9" s="109">
         <v>7</v>
       </c>
-      <c r="E9" s="143"/>
-      <c r="F9" s="164">
+      <c r="E9" s="136"/>
+      <c r="F9" s="157">
         <f>G9/D9</f>
         <v>38000</v>
       </c>
-      <c r="G9" s="162">
+      <c r="G9" s="155">
         <v>266000</v>
       </c>
-      <c r="H9" s="163"/>
-    </row>
-    <row r="10" s="100" customFormat="1" ht="40" customHeight="1" spans="1:8">
-      <c r="A10" s="117"/>
-      <c r="B10" s="118"/>
-      <c r="C10" s="115" t="s">
+      <c r="H9" s="156"/>
+    </row>
+    <row r="10" s="94" customFormat="1" ht="40" customHeight="1" spans="1:8">
+      <c r="A10" s="112"/>
+      <c r="B10" s="113"/>
+      <c r="C10" s="109" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="115">
+      <c r="D10" s="109">
         <v>5</v>
       </c>
-      <c r="E10" s="143"/>
-      <c r="F10" s="164">
+      <c r="E10" s="136"/>
+      <c r="F10" s="157">
         <f>G10/D10</f>
         <v>12500</v>
       </c>
-      <c r="G10" s="162">
+      <c r="G10" s="155">
         <v>62500</v>
       </c>
-      <c r="H10" s="163"/>
-    </row>
-    <row r="11" s="100" customFormat="1" ht="258" customHeight="1" spans="1:8">
-      <c r="A11" s="121"/>
-      <c r="B11" s="156"/>
-      <c r="C11" s="156"/>
-      <c r="D11" s="156"/>
-      <c r="E11" s="165"/>
-      <c r="F11" s="166"/>
-      <c r="G11" s="161">
+      <c r="H10" s="156"/>
+    </row>
+    <row r="11" s="94" customFormat="1" ht="258" customHeight="1" spans="1:8">
+      <c r="A11" s="116"/>
+      <c r="B11" s="119"/>
+      <c r="C11" s="119"/>
+      <c r="D11" s="119"/>
+      <c r="E11" s="139"/>
+      <c r="F11" s="158"/>
+      <c r="G11" s="154">
         <f>SUM(D11*F11)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="161">
+      <c r="H11" s="154">
         <f>SUM(G11)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" s="100" customFormat="1" ht="18" customHeight="1" spans="1:8">
-      <c r="A12" s="159" t="s">
+    <row r="12" s="94" customFormat="1" ht="18" customHeight="1" spans="1:8">
+      <c r="A12" s="152" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="160"/>
-      <c r="C12" s="160"/>
-      <c r="D12" s="160"/>
-      <c r="E12" s="160"/>
-      <c r="F12" s="160"/>
-      <c r="G12" s="167"/>
-      <c r="H12" s="168">
+      <c r="B12" s="153"/>
+      <c r="C12" s="153"/>
+      <c r="D12" s="153"/>
+      <c r="E12" s="153"/>
+      <c r="F12" s="153"/>
+      <c r="G12" s="159"/>
+      <c r="H12" s="160">
         <f>SUM(H2:H11)</f>
         <v>3291500</v>
       </c>
@@ -2553,321 +2622,408 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20.4" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="19.859375" style="103"/>
-    <col min="2" max="2" width="21.6875" style="103" customWidth="1"/>
-    <col min="3" max="3" width="43.0390625" style="103" customWidth="1"/>
-    <col min="4" max="4" width="14.4296875" style="103" customWidth="1"/>
-    <col min="5" max="5" width="58.9609375" style="104" customWidth="1"/>
-    <col min="6" max="6" width="19.5234375" style="105" customWidth="1"/>
-    <col min="7" max="7" width="20.859375" style="105" customWidth="1"/>
-    <col min="8" max="8" width="20.859375" style="106" customWidth="1"/>
-    <col min="9" max="9" width="12.859375" style="104"/>
-    <col min="10" max="16384" width="9.140625" style="104"/>
+    <col min="1" max="1" width="19.859375" style="96"/>
+    <col min="2" max="2" width="21.6875" style="96" customWidth="1"/>
+    <col min="3" max="3" width="43.0390625" style="97" customWidth="1"/>
+    <col min="4" max="4" width="14.4296875" style="96" customWidth="1"/>
+    <col min="5" max="5" width="58.9609375" style="98" customWidth="1"/>
+    <col min="6" max="6" width="19.5234375" style="99" customWidth="1"/>
+    <col min="7" max="7" width="20.859375" style="99" customWidth="1"/>
+    <col min="8" max="8" width="20.859375" style="100" customWidth="1"/>
+    <col min="9" max="9" width="12.859375" style="98"/>
+    <col min="10" max="16384" width="9.140625" style="98"/>
   </cols>
   <sheetData>
-    <row r="1" s="100" customFormat="1" ht="16" customHeight="1" spans="1:8">
-      <c r="A1" s="107" t="s">
+    <row r="1" s="94" customFormat="1" ht="16" customHeight="1" spans="1:8">
+      <c r="A1" s="101" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="108" t="s">
+      <c r="B1" s="102" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="108" t="s">
+      <c r="C1" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="108" t="s">
+      <c r="D1" s="102" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="108" t="s">
+      <c r="E1" s="102" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="134" t="s">
+      <c r="F1" s="127" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="134" t="s">
+      <c r="G1" s="127" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="135" t="s">
+      <c r="H1" s="128" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" s="100" customFormat="1" ht="130" customHeight="1" spans="1:8">
-      <c r="A2" s="109">
+    <row r="2" s="94" customFormat="1" ht="130" customHeight="1" spans="1:8">
+      <c r="A2" s="103">
         <v>46055</v>
       </c>
-      <c r="B2" s="110" t="s">
+      <c r="B2" s="104" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="111" t="s">
+      <c r="C2" s="105" t="s">
         <v>19</v>
       </c>
       <c r="D2" s="20">
         <v>2</v>
       </c>
-      <c r="E2" s="110"/>
-      <c r="F2" s="136">
+      <c r="E2" s="104"/>
+      <c r="F2" s="129">
         <v>360000</v>
       </c>
-      <c r="G2" s="136">
+      <c r="G2" s="129">
         <f>D2*F2</f>
         <v>720000</v>
       </c>
-      <c r="H2" s="137">
+      <c r="H2" s="130">
         <f>SUM(G2:G3)</f>
         <v>870000</v>
       </c>
     </row>
-    <row r="3" s="100" customFormat="1" ht="130" customHeight="1" spans="1:8">
-      <c r="A3" s="112"/>
-      <c r="B3" s="113"/>
-      <c r="C3" s="111" t="s">
+    <row r="3" s="94" customFormat="1" ht="130" customHeight="1" spans="1:8">
+      <c r="A3" s="106"/>
+      <c r="B3" s="107"/>
+      <c r="C3" s="105" t="s">
         <v>20</v>
       </c>
       <c r="D3" s="20">
         <v>6</v>
       </c>
-      <c r="E3" s="113"/>
-      <c r="F3" s="136">
+      <c r="E3" s="107"/>
+      <c r="F3" s="129">
         <v>25000</v>
       </c>
-      <c r="G3" s="136">
+      <c r="G3" s="129">
         <f>D3*F3</f>
         <v>150000</v>
       </c>
-      <c r="H3" s="138"/>
-    </row>
-    <row r="4" s="100" customFormat="1" ht="130" customHeight="1" spans="1:8">
-      <c r="A4" s="114">
+      <c r="H3" s="131"/>
+    </row>
+    <row r="4" s="94" customFormat="1" ht="130" customHeight="1" spans="1:8">
+      <c r="A4" s="108">
         <v>46056</v>
       </c>
-      <c r="B4" s="115" t="s">
+      <c r="B4" s="109" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="110" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="116">
+      <c r="D4" s="111">
         <v>3</v>
       </c>
-      <c r="E4" s="139"/>
-      <c r="F4" s="140">
+      <c r="E4" s="132"/>
+      <c r="F4" s="133">
         <v>45000</v>
       </c>
-      <c r="G4" s="141">
+      <c r="G4" s="134">
         <f>D4*F4</f>
         <v>135000</v>
       </c>
-      <c r="H4" s="142">
+      <c r="H4" s="135">
         <f>SUM(G4:G5)</f>
         <v>515000</v>
       </c>
     </row>
-    <row r="5" s="100" customFormat="1" ht="130" customHeight="1" spans="1:8">
-      <c r="A5" s="117"/>
-      <c r="B5" s="118"/>
-      <c r="C5" s="119" t="s">
+    <row r="5" s="94" customFormat="1" ht="130" customHeight="1" spans="1:8">
+      <c r="A5" s="112"/>
+      <c r="B5" s="113"/>
+      <c r="C5" s="114" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="120">
+      <c r="D5" s="115">
         <v>10</v>
       </c>
-      <c r="E5" s="143"/>
-      <c r="F5" s="142">
+      <c r="E5" s="136"/>
+      <c r="F5" s="135">
         <v>38000</v>
       </c>
-      <c r="G5" s="142">
+      <c r="G5" s="135">
         <f>D5*F5</f>
         <v>380000</v>
       </c>
-      <c r="H5" s="144"/>
-    </row>
-    <row r="6" s="101" customFormat="1" ht="208.9" customHeight="1" spans="1:8">
-      <c r="A6" s="121">
+      <c r="H5" s="137"/>
+    </row>
+    <row r="6" s="95" customFormat="1" ht="208.9" customHeight="1" spans="1:8">
+      <c r="A6" s="116">
         <v>46066</v>
       </c>
-      <c r="B6" s="122" t="s">
+      <c r="B6" s="117" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="123" t="s">
+      <c r="C6" s="118" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="116">
+      <c r="D6" s="111">
         <v>3</v>
       </c>
-      <c r="E6" s="145"/>
-      <c r="F6" s="141">
+      <c r="E6" s="138"/>
+      <c r="F6" s="134">
         <v>75000</v>
       </c>
-      <c r="G6" s="141">
+      <c r="G6" s="134">
         <f>D6*F6</f>
         <v>225000</v>
       </c>
-      <c r="H6" s="141">
+      <c r="H6" s="134">
         <f>SUM(G6)</f>
         <v>225000</v>
       </c>
     </row>
-    <row r="7" s="101" customFormat="1" ht="70" customHeight="1" spans="1:8">
-      <c r="A7" s="124">
+    <row r="7" s="95" customFormat="1" ht="70" customHeight="1" spans="1:8">
+      <c r="A7" s="116">
         <v>46069</v>
       </c>
-      <c r="B7" s="125" t="s">
+      <c r="B7" s="119" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="123" t="s">
+      <c r="C7" s="118" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="116">
+      <c r="D7" s="111">
         <v>40</v>
       </c>
-      <c r="E7" s="146"/>
-      <c r="F7" s="141">
+      <c r="E7" s="139"/>
+      <c r="F7" s="134">
         <v>35000</v>
       </c>
-      <c r="G7" s="141">
-        <f>F7*D7</f>
+      <c r="G7" s="134">
+        <f t="shared" ref="G7:G14" si="0">F7*D7</f>
         <v>1400000</v>
       </c>
-      <c r="H7" s="147">
+      <c r="H7" s="134">
         <f>SUM(G7:G9)</f>
         <v>5920000</v>
       </c>
     </row>
-    <row r="8" s="101" customFormat="1" ht="70" customHeight="1" spans="1:8">
-      <c r="A8" s="124"/>
-      <c r="B8" s="125"/>
-      <c r="C8" s="123" t="s">
+    <row r="8" s="95" customFormat="1" ht="70" customHeight="1" spans="1:8">
+      <c r="A8" s="116"/>
+      <c r="B8" s="119"/>
+      <c r="C8" s="118" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="116">
+      <c r="D8" s="111">
         <v>40</v>
       </c>
-      <c r="E8" s="146"/>
-      <c r="F8" s="141">
+      <c r="E8" s="139"/>
+      <c r="F8" s="134">
         <v>75000</v>
       </c>
-      <c r="G8" s="141">
-        <f>F8*D8</f>
+      <c r="G8" s="134">
+        <f t="shared" si="0"/>
         <v>3000000</v>
       </c>
-      <c r="H8" s="147"/>
-    </row>
-    <row r="9" s="102" customFormat="1" ht="70" customHeight="1" spans="1:8">
-      <c r="A9" s="124"/>
-      <c r="B9" s="125"/>
-      <c r="C9" s="123" t="s">
+      <c r="H8" s="134"/>
+    </row>
+    <row r="9" s="95" customFormat="1" ht="70" customHeight="1" spans="1:8">
+      <c r="A9" s="116"/>
+      <c r="B9" s="119"/>
+      <c r="C9" s="118" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="116">
+      <c r="D9" s="111">
         <v>40</v>
       </c>
-      <c r="E9" s="146"/>
-      <c r="F9" s="141">
+      <c r="E9" s="139"/>
+      <c r="F9" s="134">
         <v>38000</v>
       </c>
-      <c r="G9" s="141">
-        <f>F9*D9</f>
+      <c r="G9" s="134">
+        <f t="shared" si="0"/>
         <v>1520000</v>
       </c>
-      <c r="H9" s="147"/>
-    </row>
-    <row r="10" s="100" customFormat="1" ht="211.1" customHeight="1" spans="1:8">
-      <c r="A10" s="126">
+      <c r="H9" s="134"/>
+    </row>
+    <row r="10" s="94" customFormat="1" ht="211.1" customHeight="1" spans="1:8">
+      <c r="A10" s="120">
         <v>46070</v>
       </c>
-      <c r="B10" s="127" t="s">
+      <c r="B10" s="121" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="128" t="s">
+      <c r="C10" s="122" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="129">
+      <c r="D10" s="123">
         <v>2</v>
       </c>
-      <c r="E10" s="148"/>
-      <c r="F10" s="149">
+      <c r="E10" s="140"/>
+      <c r="F10" s="141">
         <v>295000</v>
       </c>
-      <c r="G10" s="149">
-        <f>F10*D10</f>
+      <c r="G10" s="141">
+        <f t="shared" si="0"/>
         <v>590000</v>
       </c>
-      <c r="H10" s="150">
+      <c r="H10" s="141">
         <f>SUM(G10)</f>
         <v>590000</v>
       </c>
     </row>
-    <row r="11" s="100" customFormat="1" spans="1:8">
-      <c r="A11" s="126"/>
-      <c r="B11" s="127"/>
-      <c r="C11" s="128"/>
-      <c r="D11" s="116"/>
-      <c r="E11" s="148"/>
-      <c r="F11" s="141"/>
-      <c r="G11" s="141"/>
-      <c r="H11" s="150"/>
-    </row>
-    <row r="12" s="100" customFormat="1" spans="1:8">
-      <c r="A12" s="126"/>
-      <c r="B12" s="127"/>
-      <c r="C12" s="128"/>
-      <c r="D12" s="116"/>
-      <c r="E12" s="148"/>
-      <c r="F12" s="141"/>
-      <c r="G12" s="141"/>
-      <c r="H12" s="150"/>
-    </row>
-    <row r="13" s="100" customFormat="1" spans="1:8">
-      <c r="A13" s="126"/>
-      <c r="B13" s="127"/>
-      <c r="C13" s="128"/>
-      <c r="D13" s="116"/>
-      <c r="E13" s="148"/>
-      <c r="F13" s="141"/>
-      <c r="G13" s="141"/>
-      <c r="H13" s="150"/>
-    </row>
-    <row r="14" s="100" customFormat="1" spans="1:8">
-      <c r="A14" s="130"/>
-      <c r="B14" s="131"/>
-      <c r="C14" s="132"/>
-      <c r="D14" s="116"/>
-      <c r="E14" s="151"/>
-      <c r="F14" s="140"/>
-      <c r="G14" s="141"/>
-      <c r="H14" s="149"/>
-    </row>
-    <row r="15" s="100" customFormat="1" spans="1:8">
-      <c r="A15" s="133"/>
-      <c r="B15" s="133"/>
-      <c r="C15" s="133"/>
-      <c r="D15" s="133"/>
-      <c r="E15" s="133"/>
-      <c r="F15" s="152"/>
-      <c r="G15" s="153"/>
-      <c r="H15" s="153">
-        <f>SUM(H2:H14)</f>
-        <v>8120000</v>
+    <row r="11" s="94" customFormat="1" ht="55" customHeight="1" spans="1:8">
+      <c r="A11" s="112">
+        <v>46076</v>
+      </c>
+      <c r="B11" s="113" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="122" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="111">
+        <v>10</v>
+      </c>
+      <c r="E11" s="136"/>
+      <c r="F11" s="134">
+        <v>35000</v>
+      </c>
+      <c r="G11" s="141">
+        <f t="shared" si="0"/>
+        <v>350000</v>
+      </c>
+      <c r="H11" s="142">
+        <f>SUM(G11:G14)</f>
+        <v>1955000</v>
+      </c>
+    </row>
+    <row r="12" s="94" customFormat="1" ht="55" customHeight="1" spans="1:8">
+      <c r="A12" s="112"/>
+      <c r="B12" s="113"/>
+      <c r="C12" s="122" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="111">
+        <v>10</v>
+      </c>
+      <c r="E12" s="136"/>
+      <c r="F12" s="134">
+        <v>50000</v>
+      </c>
+      <c r="G12" s="141">
+        <f t="shared" si="0"/>
+        <v>500000</v>
+      </c>
+      <c r="H12" s="142"/>
+    </row>
+    <row r="13" s="94" customFormat="1" ht="55" customHeight="1" spans="1:8">
+      <c r="A13" s="112"/>
+      <c r="B13" s="113"/>
+      <c r="C13" s="122" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="111">
+        <v>500</v>
+      </c>
+      <c r="E13" s="136"/>
+      <c r="F13" s="134">
+        <v>2000</v>
+      </c>
+      <c r="G13" s="141">
+        <f t="shared" si="0"/>
+        <v>1000000</v>
+      </c>
+      <c r="H13" s="142"/>
+    </row>
+    <row r="14" s="94" customFormat="1" ht="55" customHeight="1" spans="1:8">
+      <c r="A14" s="120"/>
+      <c r="B14" s="124"/>
+      <c r="C14" s="122" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="111">
+        <v>3</v>
+      </c>
+      <c r="E14" s="143"/>
+      <c r="F14" s="134">
+        <v>35000</v>
+      </c>
+      <c r="G14" s="141">
+        <f t="shared" si="0"/>
+        <v>105000</v>
+      </c>
+      <c r="H14" s="144"/>
+    </row>
+    <row r="15" s="94" customFormat="1" spans="1:8">
+      <c r="A15" s="120"/>
+      <c r="B15" s="121"/>
+      <c r="C15" s="122"/>
+      <c r="D15" s="111"/>
+      <c r="E15" s="140"/>
+      <c r="F15" s="134"/>
+      <c r="G15" s="134"/>
+      <c r="H15" s="141"/>
+    </row>
+    <row r="16" s="94" customFormat="1" spans="1:8">
+      <c r="A16" s="120"/>
+      <c r="B16" s="121"/>
+      <c r="C16" s="122"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="140"/>
+      <c r="F16" s="134"/>
+      <c r="G16" s="134"/>
+      <c r="H16" s="141"/>
+    </row>
+    <row r="17" s="94" customFormat="1" spans="1:8">
+      <c r="A17" s="120"/>
+      <c r="B17" s="121"/>
+      <c r="C17" s="122"/>
+      <c r="D17" s="111"/>
+      <c r="E17" s="140"/>
+      <c r="F17" s="134"/>
+      <c r="G17" s="134"/>
+      <c r="H17" s="141"/>
+    </row>
+    <row r="18" s="94" customFormat="1" spans="1:8">
+      <c r="A18" s="120"/>
+      <c r="B18" s="124"/>
+      <c r="C18" s="122"/>
+      <c r="D18" s="111"/>
+      <c r="E18" s="143"/>
+      <c r="F18" s="133"/>
+      <c r="G18" s="134"/>
+      <c r="H18" s="141"/>
+    </row>
+    <row r="19" s="94" customFormat="1" spans="1:8">
+      <c r="A19" s="125"/>
+      <c r="B19" s="125"/>
+      <c r="C19" s="126"/>
+      <c r="D19" s="125"/>
+      <c r="E19" s="125"/>
+      <c r="F19" s="145"/>
+      <c r="G19" s="146"/>
+      <c r="H19" s="146">
+        <f>SUM(H2:H18)</f>
+        <v>10075000</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A15:E15"/>
+  <mergeCells count="17">
+    <mergeCell ref="A19:E19"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A11:A14"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B11:B14"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="E7:E9"/>
+    <mergeCell ref="E11:E14"/>
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="H4:H5"/>
     <mergeCell ref="H7:H9"/>
+    <mergeCell ref="H11:H14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -2878,236 +3034,241 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.140625" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="22.5703125" customWidth="1"/>
     <col min="4" max="4" width="17.5703125" customWidth="1"/>
     <col min="5" max="5" width="34.5703125" customWidth="1"/>
     <col min="6" max="6" width="19.4296875" customWidth="1"/>
-    <col min="7" max="7" width="17.2890625" customWidth="1"/>
+    <col min="7" max="7" width="17.2890625" style="58" customWidth="1"/>
     <col min="9" max="9" width="13.0625"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1" spans="1:7">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="59" t="s">
+      <c r="B1" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="59" t="s">
+      <c r="C1" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="59" t="s">
+      <c r="D1" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="59" t="s">
+      <c r="E1" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="59" t="s">
+      <c r="F1" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="59" t="s">
+      <c r="G1" s="78" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" ht="123.5" customHeight="1" spans="1:7">
-      <c r="A2" s="60">
+      <c r="A2" s="61">
         <v>46055</v>
       </c>
       <c r="B2" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" s="61" t="s">
-        <v>33</v>
-      </c>
-      <c r="D2" s="62">
+        <v>37</v>
+      </c>
+      <c r="C2" s="62" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="63">
         <v>80</v>
       </c>
-      <c r="E2" s="81"/>
-      <c r="F2" s="82">
+      <c r="E2" s="79"/>
+      <c r="F2" s="80">
         <v>6063.9632</v>
       </c>
-      <c r="G2" s="83">
+      <c r="G2" s="81">
         <f>SUM(D2*F2)</f>
         <v>485117.056</v>
       </c>
     </row>
     <row r="3" ht="191" customHeight="1" spans="1:7">
-      <c r="A3" s="60"/>
+      <c r="A3" s="61"/>
       <c r="B3" s="47"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="83"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="81"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="60"/>
-      <c r="B4" s="65" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="65"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="66"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="86">
+      <c r="A4" s="61"/>
+      <c r="B4" s="66" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="66"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="84">
         <f>SUM(G2:G3)</f>
         <v>485117.056</v>
       </c>
-      <c r="I4" s="99"/>
+      <c r="I4" s="93"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="60"/>
-      <c r="B5" s="65" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="65"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="85"/>
-      <c r="G5" s="86">
+      <c r="A5" s="61"/>
+      <c r="B5" s="66" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="66"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="84">
         <f>G4*11%</f>
         <v>53362.87616</v>
       </c>
-      <c r="I5" s="99"/>
+      <c r="I5" s="93"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="60"/>
-      <c r="B6" s="65" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="65"/>
-      <c r="D6" s="66"/>
-      <c r="E6" s="66"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="86">
+      <c r="A6" s="61"/>
+      <c r="B6" s="66" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="66"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="84">
         <f>((G4*100)/111)*0.111%</f>
         <v>485.117056</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="60"/>
-      <c r="B7" s="65" t="s">
+      <c r="A7" s="61"/>
+      <c r="B7" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="65"/>
-      <c r="D7" s="66"/>
-      <c r="E7" s="87"/>
-      <c r="F7" s="88"/>
-      <c r="G7" s="89">
+      <c r="C7" s="66"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="85"/>
+      <c r="F7" s="86"/>
+      <c r="G7" s="84">
         <f>SUM(G4:G6)</f>
         <v>538965.049216</v>
       </c>
     </row>
-    <row r="8" ht="123.5" customHeight="1" spans="1:7">
-      <c r="A8" s="60"/>
-      <c r="B8" s="67"/>
-      <c r="C8" s="68"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="90"/>
-      <c r="F8" s="91"/>
-      <c r="G8" s="92"/>
-    </row>
-    <row r="9" ht="123.5" customHeight="1" spans="1:7">
-      <c r="A9" s="60"/>
-      <c r="B9" s="70"/>
-      <c r="C9" s="68"/>
-      <c r="D9" s="69"/>
-      <c r="E9" s="93"/>
-      <c r="F9" s="91"/>
-      <c r="G9" s="92"/>
+    <row r="8" ht="318.45" customHeight="1" spans="1:7">
+      <c r="A8" s="61">
+        <v>46072</v>
+      </c>
+      <c r="B8" s="68" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="69" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="70">
+        <v>120</v>
+      </c>
+      <c r="E8" s="49"/>
+      <c r="F8" s="87">
+        <v>6063.9632</v>
+      </c>
+      <c r="G8" s="81">
+        <f>F8*D8</f>
+        <v>727675.584</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="61"/>
+      <c r="B9" s="71" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="66"/>
+      <c r="D9" s="67"/>
+      <c r="E9" s="88"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="84">
+        <f>SUM(G8:G8)</f>
+        <v>727675.584</v>
+      </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="71"/>
-      <c r="B10" s="65" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="65"/>
-      <c r="D10" s="66"/>
-      <c r="E10" s="94"/>
-      <c r="F10" s="85"/>
-      <c r="G10" s="86">
-        <f>SUM(G8:G9)</f>
-        <v>0</v>
+      <c r="A10" s="61"/>
+      <c r="B10" s="72" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="71"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="88"/>
+      <c r="F10" s="83"/>
+      <c r="G10" s="84">
+        <f>G9*11%</f>
+        <v>80044.31424</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="72"/>
-      <c r="B11" s="73" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" s="74"/>
-      <c r="D11" s="66"/>
-      <c r="E11" s="94"/>
-      <c r="F11" s="85"/>
-      <c r="G11" s="86"/>
+      <c r="A11" s="61"/>
+      <c r="B11" s="71" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="66"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="88"/>
+      <c r="F11" s="83"/>
+      <c r="G11" s="84">
+        <f>((G9*100)/111)*0.111%</f>
+        <v>727.675584</v>
+      </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="71"/>
-      <c r="B12" s="65" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="65"/>
-      <c r="D12" s="66"/>
-      <c r="E12" s="94"/>
-      <c r="F12" s="85"/>
-      <c r="G12" s="86">
-        <f>((G10*100)/111)*0.111%</f>
-        <v>0</v>
+      <c r="A12" s="61"/>
+      <c r="B12" s="73" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="74"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="85"/>
+      <c r="F12" s="89"/>
+      <c r="G12" s="84">
+        <f>SUM(G9:G11)</f>
+        <v>808447.573824</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="75"/>
-      <c r="B13" s="76" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="77"/>
-      <c r="D13" s="66"/>
-      <c r="E13" s="87"/>
-      <c r="F13" s="95"/>
-      <c r="G13" s="89">
-        <f>SUM(G10:G12)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="78" t="s">
+      <c r="A13" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="79"/>
-      <c r="C14" s="79"/>
-      <c r="D14" s="80"/>
-      <c r="E14" s="96">
-        <f>G7+G13</f>
-        <v>538965.049216</v>
-      </c>
-      <c r="F14" s="97"/>
-      <c r="G14" s="98"/>
+      <c r="B13" s="76"/>
+      <c r="C13" s="76"/>
+      <c r="D13" s="77"/>
+      <c r="E13" s="90">
+        <f>G7+G12</f>
+        <v>1347412.62304</v>
+      </c>
+      <c r="F13" s="91"/>
+      <c r="G13" s="92"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="18">
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="E14:G14"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="E13:G13"/>
     <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A8:A12"/>
     <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B8:B9"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="E2:E3"/>
-    <mergeCell ref="E8:E9"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="G2:G3"/>
   </mergeCells>
@@ -3145,7 +3306,7 @@
         <v>7</v>
       </c>
       <c r="E1" s="45" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" s="12" customFormat="1" ht="263.65" customHeight="1" spans="1:5">
@@ -3401,10 +3562,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D1" s="17" t="s">
         <v>4</v>
@@ -3424,7 +3585,7 @@
         <v>46056</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C2" s="20">
         <v>5</v>
@@ -3447,7 +3608,7 @@
         <v>46069</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C3" s="24">
         <v>10</v>
@@ -3468,7 +3629,7 @@
     <row r="4" s="12" customFormat="1" ht="150" customHeight="1" spans="1:7">
       <c r="A4" s="26"/>
       <c r="B4" s="27" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C4" s="24">
         <v>5</v>
@@ -3540,13 +3701,13 @@
   <sheetData>
     <row r="1" ht="25" customHeight="1" spans="1:3">
       <c r="A1" s="3" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3554,7 +3715,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C2" s="8">
         <f>'Anugrah (Bag, Cup, Box)'!H12</f>
@@ -3566,11 +3727,11 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C3" s="8">
-        <f>'UD Abdi Jaya (Bag, Cup, Box)'!H15</f>
-        <v>8120000</v>
+        <f>'UD Abdi Jaya (Bag, Cup, Box)'!H19</f>
+        <v>10075000</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3578,11 +3739,11 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C4" s="8">
-        <f>'PT. SUPARMA JAYA TBK (Tissue)'!E14</f>
-        <v>538965.049216</v>
+        <f>'PT. SUPARMA JAYA TBK (Tissue)'!E13</f>
+        <v>1347412.62304</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3590,7 +3751,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C5" s="9">
         <f>'Vickel Laundry'!C32</f>
@@ -3602,7 +3763,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C6" s="9">
         <f>'Dishy Soap'!G7</f>
@@ -3616,7 +3777,7 @@
       <c r="B7" s="7"/>
       <c r="C7" s="10">
         <f>SUM(C2:C5)</f>
-        <v>11950465.049216</v>
+        <v>14713912.62304</v>
       </c>
     </row>
   </sheetData>

--- a/FEBRUARY 2026/FLOOR FEBRUARY 2026.xlsx
+++ b/FEBRUARY 2026/FLOOR FEBRUARY 2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="16360" windowHeight="18640" firstSheet="1" activeTab="1"/>
+    <workbookView windowWidth="16120" windowHeight="18640" firstSheet="3" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Anugrah (Bag, Cup, Box)" sheetId="1" r:id="rId1"/>
@@ -31,12 +31,8 @@
 </workbook>
 </file>
 
-<file path=xl/cellimages.xml><?xml version="1.0" encoding="utf-8"?>
-<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData"/>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="67">
   <si>
     <t>DATE</t>
   </si>
@@ -167,13 +163,46 @@
     <t>SO05LC2602002826/00</t>
   </si>
   <si>
-    <t>STATUS</t>
+    <t>QTY</t>
+  </si>
+  <si>
+    <t>0201</t>
+  </si>
+  <si>
+    <t>0202</t>
+  </si>
+  <si>
+    <t>0203</t>
+  </si>
+  <si>
+    <t>0204</t>
+  </si>
+  <si>
+    <t>0205</t>
+  </si>
+  <si>
+    <t>0206</t>
+  </si>
+  <si>
+    <t>0207</t>
+  </si>
+  <si>
+    <t>0208</t>
+  </si>
+  <si>
+    <t>0209</t>
+  </si>
+  <si>
+    <t>0210</t>
+  </si>
+  <si>
+    <t>0211</t>
+  </si>
+  <si>
+    <t>0212</t>
   </si>
   <si>
     <t>DESCRIPTION</t>
-  </si>
-  <si>
-    <t>QTY</t>
   </si>
   <si>
     <t>DISHY 5 L DISHWASHIG</t>
@@ -210,7 +239,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="10">
+  <numFmts count="11">
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
@@ -218,9 +247,10 @@
     <numFmt numFmtId="180" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="181" formatCode="[$-409]d\-mmm\-yyyy;@"/>
     <numFmt numFmtId="182" formatCode="[$Rp-421]#,##0.00;[Red][$Rp-421]#,##0.00"/>
-    <numFmt numFmtId="183" formatCode="dd\-mmm"/>
-    <numFmt numFmtId="184" formatCode="_ [$IDR]\ * #,##0_ ;_ [$IDR]\ * \-#,##0_ ;_ [$IDR]\ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="185" formatCode="[$Rp-421]#,##0.0000;[Red][$Rp-421]#,##0.0000"/>
+    <numFmt numFmtId="183" formatCode="0;[Red]0"/>
+    <numFmt numFmtId="184" formatCode="dd\-mmm"/>
+    <numFmt numFmtId="185" formatCode="_ [$IDR]\ * #,##0_ ;_ [$IDR]\ * \-#,##0_ ;_ [$IDR]\ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="186" formatCode="[$Rp-421]#,##0.0000;[Red][$Rp-421]#,##0.0000"/>
   </numFmts>
   <fonts count="33">
     <font>
@@ -1089,7 +1119,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="161">
+  <cellXfs count="162">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1217,25 +1247,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="185" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="185" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1244,17 +1280,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1284,7 +1314,7 @@
     <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="183" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="184" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1320,28 +1350,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="185" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="186" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="185" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="185" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="186" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="186" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="185" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="185" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="186" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="186" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="185" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="186" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="180" fontId="8" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1522,13 +1555,13 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="184" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="9" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="185" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="185" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="185" fontId="9" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1542,6 +1575,9 @@
     </xf>
     <xf numFmtId="180" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1635,7 +1671,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7257415" y="230505"/>
+          <a:off x="6833870" y="230505"/>
           <a:ext cx="2531110" cy="3516630"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1674,7 +1710,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7263130" y="3786505"/>
+          <a:off x="6839585" y="3786505"/>
           <a:ext cx="2519680" cy="3517265"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2347,256 +2383,256 @@
   <dimension ref="A1:H12"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20.4" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="17.4296875" style="98"/>
-    <col min="2" max="2" width="13.4296875" style="98" customWidth="1"/>
-    <col min="3" max="3" width="36" style="98" customWidth="1"/>
-    <col min="4" max="4" width="21.2890625" style="96" customWidth="1"/>
-    <col min="5" max="5" width="33.2890625" style="98" customWidth="1"/>
-    <col min="6" max="6" width="17.2890625" style="98" customWidth="1"/>
-    <col min="7" max="8" width="20.859375" style="98" customWidth="1"/>
-    <col min="9" max="9" width="12.859375" style="98"/>
-    <col min="10" max="10" width="15" style="98"/>
-    <col min="11" max="16384" width="18.0390625" style="98"/>
+    <col min="1" max="1" width="13.25" style="99" customWidth="1"/>
+    <col min="2" max="2" width="13.4296875" style="99" customWidth="1"/>
+    <col min="3" max="3" width="34.96875" style="99" customWidth="1"/>
+    <col min="4" max="4" width="21.2890625" style="97" customWidth="1"/>
+    <col min="5" max="5" width="33.2890625" style="99" customWidth="1"/>
+    <col min="6" max="6" width="17.2890625" style="99" customWidth="1"/>
+    <col min="7" max="8" width="20.859375" style="99" customWidth="1"/>
+    <col min="9" max="9" width="12.859375" style="99"/>
+    <col min="10" max="10" width="15" style="99"/>
+    <col min="11" max="16384" width="18.0390625" style="99"/>
   </cols>
   <sheetData>
-    <row r="1" s="94" customFormat="1" ht="16" customHeight="1" spans="1:8">
-      <c r="A1" s="147" t="s">
+    <row r="1" s="95" customFormat="1" ht="16" customHeight="1" spans="1:8">
+      <c r="A1" s="148" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="148" t="s">
+      <c r="B1" s="149" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="148" t="s">
+      <c r="C1" s="149" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="148" t="s">
+      <c r="D1" s="149" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="148" t="s">
+      <c r="E1" s="149" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="148" t="s">
+      <c r="F1" s="149" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="148" t="s">
+      <c r="G1" s="149" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="148" t="s">
+      <c r="H1" s="149" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" s="94" customFormat="1" ht="140" customHeight="1" spans="1:8">
-      <c r="A2" s="108">
+    <row r="2" s="95" customFormat="1" ht="140" customHeight="1" spans="1:8">
+      <c r="A2" s="109">
         <v>46056</v>
       </c>
-      <c r="B2" s="119">
+      <c r="B2" s="120">
         <v>3426</v>
       </c>
-      <c r="C2" s="149" t="s">
+      <c r="C2" s="150" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="150">
+      <c r="D2" s="151">
         <v>20</v>
       </c>
-      <c r="E2" s="132"/>
-      <c r="F2" s="154">
+      <c r="E2" s="133"/>
+      <c r="F2" s="155">
         <v>55000</v>
       </c>
-      <c r="G2" s="155">
+      <c r="G2" s="156">
         <f>SUM(D2*F2)</f>
         <v>1100000</v>
       </c>
-      <c r="H2" s="155">
+      <c r="H2" s="156">
         <f>SUM(G2:G3)</f>
         <v>1650000</v>
       </c>
     </row>
-    <row r="3" s="94" customFormat="1" ht="140" customHeight="1" spans="1:8">
-      <c r="A3" s="112"/>
-      <c r="B3" s="119"/>
-      <c r="C3" s="149" t="s">
+    <row r="3" s="95" customFormat="1" ht="140" customHeight="1" spans="1:8">
+      <c r="A3" s="113"/>
+      <c r="B3" s="120"/>
+      <c r="C3" s="150" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="150">
+      <c r="D3" s="151">
         <v>10</v>
       </c>
-      <c r="E3" s="136"/>
-      <c r="F3" s="154">
+      <c r="E3" s="137"/>
+      <c r="F3" s="155">
         <v>55000</v>
       </c>
-      <c r="G3" s="155">
+      <c r="G3" s="156">
         <f>SUM(D3*F3)</f>
         <v>550000</v>
       </c>
-      <c r="H3" s="156"/>
-    </row>
-    <row r="4" s="94" customFormat="1" ht="40" customHeight="1" spans="1:8">
-      <c r="A4" s="108">
+      <c r="H3" s="157"/>
+    </row>
+    <row r="4" s="95" customFormat="1" ht="40" customHeight="1" spans="1:8">
+      <c r="A4" s="109">
         <v>46058</v>
       </c>
-      <c r="B4" s="109">
+      <c r="B4" s="110">
         <v>3461</v>
       </c>
-      <c r="C4" s="151" t="s">
+      <c r="C4" s="152" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="150">
+      <c r="D4" s="151">
         <v>450</v>
       </c>
-      <c r="E4" s="132"/>
-      <c r="F4" s="155">
+      <c r="E4" s="133"/>
+      <c r="F4" s="156">
         <v>1800</v>
       </c>
-      <c r="G4" s="155">
+      <c r="G4" s="156">
         <f>SUM(D4*F4)</f>
         <v>810000</v>
       </c>
-      <c r="H4" s="155">
+      <c r="H4" s="156">
         <f>SUM(G4:G10)</f>
         <v>1641500</v>
       </c>
     </row>
-    <row r="5" s="94" customFormat="1" ht="40" customHeight="1" spans="1:8">
-      <c r="A5" s="112"/>
-      <c r="B5" s="113"/>
-      <c r="C5" s="119" t="s">
+    <row r="5" s="95" customFormat="1" ht="40" customHeight="1" spans="1:8">
+      <c r="A5" s="113"/>
+      <c r="B5" s="114"/>
+      <c r="C5" s="120" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="119">
+      <c r="D5" s="120">
         <v>100</v>
       </c>
-      <c r="E5" s="136"/>
-      <c r="F5" s="157">
+      <c r="E5" s="137"/>
+      <c r="F5" s="158">
         <v>630</v>
       </c>
-      <c r="G5" s="155">
+      <c r="G5" s="156">
         <f>SUM(D5*F5)</f>
         <v>63000</v>
       </c>
-      <c r="H5" s="156"/>
-    </row>
-    <row r="6" s="94" customFormat="1" ht="40" customHeight="1" spans="1:8">
-      <c r="A6" s="112"/>
-      <c r="B6" s="113"/>
-      <c r="C6" s="119" t="s">
+      <c r="H5" s="157"/>
+    </row>
+    <row r="6" s="95" customFormat="1" ht="40" customHeight="1" spans="1:8">
+      <c r="A6" s="113"/>
+      <c r="B6" s="114"/>
+      <c r="C6" s="120" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="119">
+      <c r="D6" s="120">
         <v>36</v>
       </c>
-      <c r="E6" s="136"/>
-      <c r="F6" s="157">
+      <c r="E6" s="137"/>
+      <c r="F6" s="158">
         <f>G6/D6</f>
         <v>3166.66666666667</v>
       </c>
-      <c r="G6" s="155">
+      <c r="G6" s="156">
         <v>114000</v>
       </c>
-      <c r="H6" s="156"/>
-    </row>
-    <row r="7" s="94" customFormat="1" ht="40" customHeight="1" spans="1:8">
-      <c r="A7" s="112"/>
-      <c r="B7" s="113"/>
-      <c r="C7" s="109" t="s">
+      <c r="H6" s="157"/>
+    </row>
+    <row r="7" s="95" customFormat="1" ht="40" customHeight="1" spans="1:8">
+      <c r="A7" s="113"/>
+      <c r="B7" s="114"/>
+      <c r="C7" s="110" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="109">
+      <c r="D7" s="110">
         <v>36</v>
       </c>
-      <c r="E7" s="136"/>
-      <c r="F7" s="157">
+      <c r="E7" s="137"/>
+      <c r="F7" s="158">
         <f>G7/D7</f>
         <v>2666.66666666667</v>
       </c>
-      <c r="G7" s="155">
+      <c r="G7" s="156">
         <v>96000</v>
       </c>
-      <c r="H7" s="156"/>
-    </row>
-    <row r="8" s="94" customFormat="1" ht="40" customHeight="1" spans="1:8">
-      <c r="A8" s="112"/>
-      <c r="B8" s="113"/>
-      <c r="C8" s="109" t="s">
+      <c r="H7" s="157"/>
+    </row>
+    <row r="8" s="95" customFormat="1" ht="40" customHeight="1" spans="1:8">
+      <c r="A8" s="113"/>
+      <c r="B8" s="114"/>
+      <c r="C8" s="110" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="109">
+      <c r="D8" s="110">
         <v>10</v>
       </c>
-      <c r="E8" s="136"/>
-      <c r="F8" s="157">
+      <c r="E8" s="137"/>
+      <c r="F8" s="158">
         <v>23000</v>
       </c>
-      <c r="G8" s="155">
+      <c r="G8" s="156">
         <f>F8*D8</f>
         <v>230000</v>
       </c>
-      <c r="H8" s="156"/>
-    </row>
-    <row r="9" s="94" customFormat="1" ht="40" customHeight="1" spans="1:8">
-      <c r="A9" s="112"/>
-      <c r="B9" s="113"/>
-      <c r="C9" s="109" t="s">
+      <c r="H8" s="157"/>
+    </row>
+    <row r="9" s="95" customFormat="1" ht="40" customHeight="1" spans="1:8">
+      <c r="A9" s="113"/>
+      <c r="B9" s="114"/>
+      <c r="C9" s="110" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="109">
+      <c r="D9" s="110">
         <v>7</v>
       </c>
-      <c r="E9" s="136"/>
-      <c r="F9" s="157">
+      <c r="E9" s="137"/>
+      <c r="F9" s="158">
         <f>G9/D9</f>
         <v>38000</v>
       </c>
-      <c r="G9" s="155">
+      <c r="G9" s="156">
         <v>266000</v>
       </c>
-      <c r="H9" s="156"/>
-    </row>
-    <row r="10" s="94" customFormat="1" ht="40" customHeight="1" spans="1:8">
-      <c r="A10" s="112"/>
-      <c r="B10" s="113"/>
-      <c r="C10" s="109" t="s">
+      <c r="H9" s="157"/>
+    </row>
+    <row r="10" s="95" customFormat="1" ht="40" customHeight="1" spans="1:8">
+      <c r="A10" s="113"/>
+      <c r="B10" s="114"/>
+      <c r="C10" s="110" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="109">
+      <c r="D10" s="110">
         <v>5</v>
       </c>
-      <c r="E10" s="136"/>
-      <c r="F10" s="157">
+      <c r="E10" s="137"/>
+      <c r="F10" s="158">
         <f>G10/D10</f>
         <v>12500</v>
       </c>
-      <c r="G10" s="155">
+      <c r="G10" s="156">
         <v>62500</v>
       </c>
-      <c r="H10" s="156"/>
-    </row>
-    <row r="11" s="94" customFormat="1" ht="258" customHeight="1" spans="1:8">
-      <c r="A11" s="116"/>
-      <c r="B11" s="119"/>
-      <c r="C11" s="119"/>
-      <c r="D11" s="119"/>
-      <c r="E11" s="139"/>
-      <c r="F11" s="158"/>
-      <c r="G11" s="154">
+      <c r="H10" s="157"/>
+    </row>
+    <row r="11" s="95" customFormat="1" ht="258" customHeight="1" spans="1:8">
+      <c r="A11" s="117"/>
+      <c r="B11" s="120"/>
+      <c r="C11" s="120"/>
+      <c r="D11" s="120"/>
+      <c r="E11" s="140"/>
+      <c r="F11" s="159"/>
+      <c r="G11" s="155">
         <f>SUM(D11*F11)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="154">
+      <c r="H11" s="155">
         <f>SUM(G11)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" s="94" customFormat="1" ht="18" customHeight="1" spans="1:8">
-      <c r="A12" s="152" t="s">
+    <row r="12" s="95" customFormat="1" ht="18" customHeight="1" spans="1:8">
+      <c r="A12" s="153" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="153"/>
-      <c r="C12" s="153"/>
-      <c r="D12" s="153"/>
-      <c r="E12" s="153"/>
-      <c r="F12" s="153"/>
-      <c r="G12" s="159"/>
-      <c r="H12" s="160">
+      <c r="B12" s="154"/>
+      <c r="C12" s="154"/>
+      <c r="D12" s="154"/>
+      <c r="E12" s="154"/>
+      <c r="F12" s="154"/>
+      <c r="G12" s="160"/>
+      <c r="H12" s="161">
         <f>SUM(H2:H11)</f>
         <v>3291500</v>
       </c>
@@ -2625,382 +2661,382 @@
   <dimension ref="A1:H19"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20.4" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="19.859375" style="96"/>
-    <col min="2" max="2" width="21.6875" style="96" customWidth="1"/>
-    <col min="3" max="3" width="43.0390625" style="97" customWidth="1"/>
-    <col min="4" max="4" width="14.4296875" style="96" customWidth="1"/>
-    <col min="5" max="5" width="58.9609375" style="98" customWidth="1"/>
-    <col min="6" max="6" width="19.5234375" style="99" customWidth="1"/>
-    <col min="7" max="7" width="20.859375" style="99" customWidth="1"/>
-    <col min="8" max="8" width="20.859375" style="100" customWidth="1"/>
-    <col min="9" max="9" width="12.859375" style="98"/>
-    <col min="10" max="16384" width="9.140625" style="98"/>
+    <col min="1" max="1" width="19.859375" style="97"/>
+    <col min="2" max="2" width="21.6875" style="97" customWidth="1"/>
+    <col min="3" max="3" width="43.0390625" style="98" customWidth="1"/>
+    <col min="4" max="4" width="14.4296875" style="97" customWidth="1"/>
+    <col min="5" max="5" width="58.9609375" style="99" customWidth="1"/>
+    <col min="6" max="6" width="19.5234375" style="100" customWidth="1"/>
+    <col min="7" max="7" width="20.859375" style="100" customWidth="1"/>
+    <col min="8" max="8" width="20.859375" style="101" customWidth="1"/>
+    <col min="9" max="9" width="12.859375" style="99"/>
+    <col min="10" max="16384" width="9.140625" style="99"/>
   </cols>
   <sheetData>
-    <row r="1" s="94" customFormat="1" ht="16" customHeight="1" spans="1:8">
-      <c r="A1" s="101" t="s">
+    <row r="1" s="95" customFormat="1" ht="16" customHeight="1" spans="1:8">
+      <c r="A1" s="102" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="102" t="s">
+      <c r="B1" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="102" t="s">
+      <c r="C1" s="103" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="102" t="s">
+      <c r="D1" s="103" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="102" t="s">
+      <c r="E1" s="103" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="127" t="s">
+      <c r="F1" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="127" t="s">
+      <c r="G1" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="128" t="s">
+      <c r="H1" s="129" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" s="94" customFormat="1" ht="130" customHeight="1" spans="1:8">
-      <c r="A2" s="103">
+    <row r="2" s="95" customFormat="1" ht="130" customHeight="1" spans="1:8">
+      <c r="A2" s="104">
         <v>46055</v>
       </c>
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="105" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="105" t="s">
+      <c r="C2" s="106" t="s">
         <v>19</v>
       </c>
       <c r="D2" s="20">
         <v>2</v>
       </c>
-      <c r="E2" s="104"/>
-      <c r="F2" s="129">
+      <c r="E2" s="105"/>
+      <c r="F2" s="130">
         <v>360000</v>
       </c>
-      <c r="G2" s="129">
+      <c r="G2" s="130">
         <f>D2*F2</f>
         <v>720000</v>
       </c>
-      <c r="H2" s="130">
+      <c r="H2" s="131">
         <f>SUM(G2:G3)</f>
         <v>870000</v>
       </c>
     </row>
-    <row r="3" s="94" customFormat="1" ht="130" customHeight="1" spans="1:8">
-      <c r="A3" s="106"/>
-      <c r="B3" s="107"/>
-      <c r="C3" s="105" t="s">
+    <row r="3" s="95" customFormat="1" ht="130" customHeight="1" spans="1:8">
+      <c r="A3" s="107"/>
+      <c r="B3" s="108"/>
+      <c r="C3" s="106" t="s">
         <v>20</v>
       </c>
       <c r="D3" s="20">
         <v>6</v>
       </c>
-      <c r="E3" s="107"/>
-      <c r="F3" s="129">
+      <c r="E3" s="108"/>
+      <c r="F3" s="130">
         <v>25000</v>
       </c>
-      <c r="G3" s="129">
+      <c r="G3" s="130">
         <f>D3*F3</f>
         <v>150000</v>
       </c>
-      <c r="H3" s="131"/>
-    </row>
-    <row r="4" s="94" customFormat="1" ht="130" customHeight="1" spans="1:8">
-      <c r="A4" s="108">
+      <c r="H3" s="132"/>
+    </row>
+    <row r="4" s="95" customFormat="1" ht="130" customHeight="1" spans="1:8">
+      <c r="A4" s="109">
         <v>46056</v>
       </c>
-      <c r="B4" s="109" t="s">
+      <c r="B4" s="110" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="110" t="s">
+      <c r="C4" s="111" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="111">
+      <c r="D4" s="112">
         <v>3</v>
       </c>
-      <c r="E4" s="132"/>
-      <c r="F4" s="133">
+      <c r="E4" s="133"/>
+      <c r="F4" s="134">
         <v>45000</v>
       </c>
-      <c r="G4" s="134">
+      <c r="G4" s="135">
         <f>D4*F4</f>
         <v>135000</v>
       </c>
-      <c r="H4" s="135">
+      <c r="H4" s="136">
         <f>SUM(G4:G5)</f>
         <v>515000</v>
       </c>
     </row>
-    <row r="5" s="94" customFormat="1" ht="130" customHeight="1" spans="1:8">
-      <c r="A5" s="112"/>
-      <c r="B5" s="113"/>
-      <c r="C5" s="114" t="s">
+    <row r="5" s="95" customFormat="1" ht="130" customHeight="1" spans="1:8">
+      <c r="A5" s="113"/>
+      <c r="B5" s="114"/>
+      <c r="C5" s="115" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="115">
+      <c r="D5" s="116">
         <v>10</v>
       </c>
-      <c r="E5" s="136"/>
-      <c r="F5" s="135">
+      <c r="E5" s="137"/>
+      <c r="F5" s="136">
         <v>38000</v>
       </c>
-      <c r="G5" s="135">
+      <c r="G5" s="136">
         <f>D5*F5</f>
         <v>380000</v>
       </c>
-      <c r="H5" s="137"/>
-    </row>
-    <row r="6" s="95" customFormat="1" ht="208.9" customHeight="1" spans="1:8">
-      <c r="A6" s="116">
+      <c r="H5" s="138"/>
+    </row>
+    <row r="6" s="96" customFormat="1" ht="208.9" customHeight="1" spans="1:8">
+      <c r="A6" s="117">
         <v>46066</v>
       </c>
-      <c r="B6" s="117" t="s">
+      <c r="B6" s="118" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="118" t="s">
+      <c r="C6" s="119" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="111">
+      <c r="D6" s="112">
         <v>3</v>
       </c>
-      <c r="E6" s="138"/>
-      <c r="F6" s="134">
+      <c r="E6" s="139"/>
+      <c r="F6" s="135">
         <v>75000</v>
       </c>
-      <c r="G6" s="134">
+      <c r="G6" s="135">
         <f>D6*F6</f>
         <v>225000</v>
       </c>
-      <c r="H6" s="134">
+      <c r="H6" s="135">
         <f>SUM(G6)</f>
         <v>225000</v>
       </c>
     </row>
-    <row r="7" s="95" customFormat="1" ht="70" customHeight="1" spans="1:8">
-      <c r="A7" s="116">
+    <row r="7" s="96" customFormat="1" ht="70" customHeight="1" spans="1:8">
+      <c r="A7" s="117">
         <v>46069</v>
       </c>
-      <c r="B7" s="119" t="s">
+      <c r="B7" s="120" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="118" t="s">
+      <c r="C7" s="119" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="111">
+      <c r="D7" s="112">
         <v>40</v>
       </c>
-      <c r="E7" s="139"/>
-      <c r="F7" s="134">
+      <c r="E7" s="140"/>
+      <c r="F7" s="135">
         <v>35000</v>
       </c>
-      <c r="G7" s="134">
+      <c r="G7" s="135">
         <f t="shared" ref="G7:G14" si="0">F7*D7</f>
         <v>1400000</v>
       </c>
-      <c r="H7" s="134">
+      <c r="H7" s="135">
         <f>SUM(G7:G9)</f>
         <v>5920000</v>
       </c>
     </row>
-    <row r="8" s="95" customFormat="1" ht="70" customHeight="1" spans="1:8">
-      <c r="A8" s="116"/>
-      <c r="B8" s="119"/>
-      <c r="C8" s="118" t="s">
+    <row r="8" s="96" customFormat="1" ht="70" customHeight="1" spans="1:8">
+      <c r="A8" s="117"/>
+      <c r="B8" s="120"/>
+      <c r="C8" s="119" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="111">
+      <c r="D8" s="112">
         <v>40</v>
       </c>
-      <c r="E8" s="139"/>
-      <c r="F8" s="134">
+      <c r="E8" s="140"/>
+      <c r="F8" s="135">
         <v>75000</v>
       </c>
-      <c r="G8" s="134">
+      <c r="G8" s="135">
         <f t="shared" si="0"/>
         <v>3000000</v>
       </c>
-      <c r="H8" s="134"/>
-    </row>
-    <row r="9" s="95" customFormat="1" ht="70" customHeight="1" spans="1:8">
-      <c r="A9" s="116"/>
-      <c r="B9" s="119"/>
-      <c r="C9" s="118" t="s">
+      <c r="H8" s="135"/>
+    </row>
+    <row r="9" s="96" customFormat="1" ht="70" customHeight="1" spans="1:8">
+      <c r="A9" s="117"/>
+      <c r="B9" s="120"/>
+      <c r="C9" s="119" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="111">
+      <c r="D9" s="112">
         <v>40</v>
       </c>
-      <c r="E9" s="139"/>
-      <c r="F9" s="134">
+      <c r="E9" s="140"/>
+      <c r="F9" s="135">
         <v>38000</v>
       </c>
-      <c r="G9" s="134">
+      <c r="G9" s="135">
         <f t="shared" si="0"/>
         <v>1520000</v>
       </c>
-      <c r="H9" s="134"/>
-    </row>
-    <row r="10" s="94" customFormat="1" ht="211.1" customHeight="1" spans="1:8">
-      <c r="A10" s="120">
+      <c r="H9" s="135"/>
+    </row>
+    <row r="10" s="95" customFormat="1" ht="211.1" customHeight="1" spans="1:8">
+      <c r="A10" s="121">
         <v>46070</v>
       </c>
-      <c r="B10" s="121" t="s">
+      <c r="B10" s="122" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="122" t="s">
+      <c r="C10" s="123" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="123">
+      <c r="D10" s="124">
         <v>2</v>
       </c>
-      <c r="E10" s="140"/>
-      <c r="F10" s="141">
+      <c r="E10" s="141"/>
+      <c r="F10" s="142">
         <v>295000</v>
       </c>
-      <c r="G10" s="141">
+      <c r="G10" s="142">
         <f t="shared" si="0"/>
         <v>590000</v>
       </c>
-      <c r="H10" s="141">
+      <c r="H10" s="142">
         <f>SUM(G10)</f>
         <v>590000</v>
       </c>
     </row>
-    <row r="11" s="94" customFormat="1" ht="55" customHeight="1" spans="1:8">
-      <c r="A11" s="112">
+    <row r="11" s="95" customFormat="1" ht="55" customHeight="1" spans="1:8">
+      <c r="A11" s="113">
         <v>46076</v>
       </c>
-      <c r="B11" s="113" t="s">
+      <c r="B11" s="114" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="122" t="s">
+      <c r="C11" s="123" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="111">
+      <c r="D11" s="112">
         <v>10</v>
       </c>
-      <c r="E11" s="136"/>
-      <c r="F11" s="134">
+      <c r="E11" s="137"/>
+      <c r="F11" s="135">
         <v>35000</v>
       </c>
-      <c r="G11" s="141">
+      <c r="G11" s="142">
         <f t="shared" si="0"/>
         <v>350000</v>
       </c>
-      <c r="H11" s="142">
+      <c r="H11" s="143">
         <f>SUM(G11:G14)</f>
         <v>1955000</v>
       </c>
     </row>
-    <row r="12" s="94" customFormat="1" ht="55" customHeight="1" spans="1:8">
-      <c r="A12" s="112"/>
-      <c r="B12" s="113"/>
-      <c r="C12" s="122" t="s">
+    <row r="12" s="95" customFormat="1" ht="55" customHeight="1" spans="1:8">
+      <c r="A12" s="113"/>
+      <c r="B12" s="114"/>
+      <c r="C12" s="123" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="111">
+      <c r="D12" s="112">
         <v>10</v>
       </c>
-      <c r="E12" s="136"/>
-      <c r="F12" s="134">
+      <c r="E12" s="137"/>
+      <c r="F12" s="135">
         <v>50000</v>
       </c>
-      <c r="G12" s="141">
+      <c r="G12" s="142">
         <f t="shared" si="0"/>
         <v>500000</v>
       </c>
-      <c r="H12" s="142"/>
-    </row>
-    <row r="13" s="94" customFormat="1" ht="55" customHeight="1" spans="1:8">
-      <c r="A13" s="112"/>
-      <c r="B13" s="113"/>
-      <c r="C13" s="122" t="s">
+      <c r="H12" s="143"/>
+    </row>
+    <row r="13" s="95" customFormat="1" ht="55" customHeight="1" spans="1:8">
+      <c r="A13" s="113"/>
+      <c r="B13" s="114"/>
+      <c r="C13" s="123" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="111">
+      <c r="D13" s="112">
         <v>500</v>
       </c>
-      <c r="E13" s="136"/>
-      <c r="F13" s="134">
+      <c r="E13" s="137"/>
+      <c r="F13" s="135">
         <v>2000</v>
       </c>
-      <c r="G13" s="141">
+      <c r="G13" s="142">
         <f t="shared" si="0"/>
         <v>1000000</v>
       </c>
-      <c r="H13" s="142"/>
-    </row>
-    <row r="14" s="94" customFormat="1" ht="55" customHeight="1" spans="1:8">
-      <c r="A14" s="120"/>
-      <c r="B14" s="124"/>
-      <c r="C14" s="122" t="s">
+      <c r="H13" s="143"/>
+    </row>
+    <row r="14" s="95" customFormat="1" ht="55" customHeight="1" spans="1:8">
+      <c r="A14" s="121"/>
+      <c r="B14" s="125"/>
+      <c r="C14" s="123" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="111">
+      <c r="D14" s="112">
         <v>3</v>
       </c>
-      <c r="E14" s="143"/>
-      <c r="F14" s="134">
+      <c r="E14" s="144"/>
+      <c r="F14" s="135">
         <v>35000</v>
       </c>
-      <c r="G14" s="141">
+      <c r="G14" s="142">
         <f t="shared" si="0"/>
         <v>105000</v>
       </c>
-      <c r="H14" s="144"/>
-    </row>
-    <row r="15" s="94" customFormat="1" spans="1:8">
-      <c r="A15" s="120"/>
-      <c r="B15" s="121"/>
-      <c r="C15" s="122"/>
-      <c r="D15" s="111"/>
-      <c r="E15" s="140"/>
-      <c r="F15" s="134"/>
-      <c r="G15" s="134"/>
-      <c r="H15" s="141"/>
-    </row>
-    <row r="16" s="94" customFormat="1" spans="1:8">
-      <c r="A16" s="120"/>
-      <c r="B16" s="121"/>
-      <c r="C16" s="122"/>
-      <c r="D16" s="111"/>
-      <c r="E16" s="140"/>
-      <c r="F16" s="134"/>
-      <c r="G16" s="134"/>
-      <c r="H16" s="141"/>
-    </row>
-    <row r="17" s="94" customFormat="1" spans="1:8">
-      <c r="A17" s="120"/>
-      <c r="B17" s="121"/>
-      <c r="C17" s="122"/>
-      <c r="D17" s="111"/>
-      <c r="E17" s="140"/>
-      <c r="F17" s="134"/>
-      <c r="G17" s="134"/>
-      <c r="H17" s="141"/>
-    </row>
-    <row r="18" s="94" customFormat="1" spans="1:8">
-      <c r="A18" s="120"/>
-      <c r="B18" s="124"/>
-      <c r="C18" s="122"/>
-      <c r="D18" s="111"/>
-      <c r="E18" s="143"/>
-      <c r="F18" s="133"/>
-      <c r="G18" s="134"/>
-      <c r="H18" s="141"/>
-    </row>
-    <row r="19" s="94" customFormat="1" spans="1:8">
-      <c r="A19" s="125"/>
-      <c r="B19" s="125"/>
-      <c r="C19" s="126"/>
-      <c r="D19" s="125"/>
-      <c r="E19" s="125"/>
-      <c r="F19" s="145"/>
-      <c r="G19" s="146"/>
-      <c r="H19" s="146">
+      <c r="H14" s="145"/>
+    </row>
+    <row r="15" s="95" customFormat="1" spans="1:8">
+      <c r="A15" s="121"/>
+      <c r="B15" s="122"/>
+      <c r="C15" s="123"/>
+      <c r="D15" s="112"/>
+      <c r="E15" s="141"/>
+      <c r="F15" s="135"/>
+      <c r="G15" s="135"/>
+      <c r="H15" s="142"/>
+    </row>
+    <row r="16" s="95" customFormat="1" spans="1:8">
+      <c r="A16" s="121"/>
+      <c r="B16" s="122"/>
+      <c r="C16" s="123"/>
+      <c r="D16" s="112"/>
+      <c r="E16" s="141"/>
+      <c r="F16" s="135"/>
+      <c r="G16" s="135"/>
+      <c r="H16" s="142"/>
+    </row>
+    <row r="17" s="95" customFormat="1" spans="1:8">
+      <c r="A17" s="121"/>
+      <c r="B17" s="122"/>
+      <c r="C17" s="123"/>
+      <c r="D17" s="112"/>
+      <c r="E17" s="141"/>
+      <c r="F17" s="135"/>
+      <c r="G17" s="135"/>
+      <c r="H17" s="142"/>
+    </row>
+    <row r="18" s="95" customFormat="1" spans="1:8">
+      <c r="A18" s="121"/>
+      <c r="B18" s="125"/>
+      <c r="C18" s="123"/>
+      <c r="D18" s="112"/>
+      <c r="E18" s="144"/>
+      <c r="F18" s="134"/>
+      <c r="G18" s="135"/>
+      <c r="H18" s="142"/>
+    </row>
+    <row r="19" s="95" customFormat="1" spans="1:8">
+      <c r="A19" s="126"/>
+      <c r="B19" s="126"/>
+      <c r="C19" s="127"/>
+      <c r="D19" s="126"/>
+      <c r="E19" s="126"/>
+      <c r="F19" s="146"/>
+      <c r="G19" s="147"/>
+      <c r="H19" s="147">
         <f>SUM(H2:H18)</f>
         <v>10075000</v>
       </c>
@@ -3074,7 +3110,7 @@
       <c r="A2" s="61">
         <v>46055</v>
       </c>
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="49" t="s">
         <v>37</v>
       </c>
       <c r="C2" s="62" t="s">
@@ -3094,7 +3130,7 @@
     </row>
     <row r="3" ht="191" customHeight="1" spans="1:7">
       <c r="A3" s="61"/>
-      <c r="B3" s="47"/>
+      <c r="B3" s="49"/>
       <c r="C3" s="64"/>
       <c r="D3" s="65"/>
       <c r="E3" s="79"/>
@@ -3114,7 +3150,7 @@
         <f>SUM(G2:G3)</f>
         <v>485117.056</v>
       </c>
-      <c r="I4" s="93"/>
+      <c r="I4" s="94"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="61"/>
@@ -3129,7 +3165,7 @@
         <f>G4*11%</f>
         <v>53362.87616</v>
       </c>
-      <c r="I5" s="93"/>
+      <c r="I5" s="94"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="61"/>
@@ -3172,8 +3208,8 @@
       <c r="D8" s="70">
         <v>120</v>
       </c>
-      <c r="E8" s="49"/>
-      <c r="F8" s="87">
+      <c r="E8" s="87"/>
+      <c r="F8" s="88">
         <v>6063.9632</v>
       </c>
       <c r="G8" s="81">
@@ -3188,7 +3224,7 @@
       </c>
       <c r="C9" s="66"/>
       <c r="D9" s="67"/>
-      <c r="E9" s="88"/>
+      <c r="E9" s="89"/>
       <c r="F9" s="83"/>
       <c r="G9" s="84">
         <f>SUM(G8:G8)</f>
@@ -3202,7 +3238,7 @@
       </c>
       <c r="C10" s="71"/>
       <c r="D10" s="67"/>
-      <c r="E10" s="88"/>
+      <c r="E10" s="89"/>
       <c r="F10" s="83"/>
       <c r="G10" s="84">
         <f>G9*11%</f>
@@ -3216,7 +3252,7 @@
       </c>
       <c r="C11" s="66"/>
       <c r="D11" s="67"/>
-      <c r="E11" s="88"/>
+      <c r="E11" s="89"/>
       <c r="F11" s="83"/>
       <c r="G11" s="84">
         <f>((G9*100)/111)*0.111%</f>
@@ -3231,7 +3267,7 @@
       <c r="C12" s="74"/>
       <c r="D12" s="67"/>
       <c r="E12" s="85"/>
-      <c r="F12" s="89"/>
+      <c r="F12" s="90"/>
       <c r="G12" s="84">
         <f>SUM(G9:G11)</f>
         <v>808447.573824</v>
@@ -3244,12 +3280,11 @@
       <c r="B13" s="76"/>
       <c r="C13" s="76"/>
       <c r="D13" s="77"/>
-      <c r="E13" s="90">
-        <f>G7+G12</f>
-        <v>1347412.62304</v>
-      </c>
-      <c r="F13" s="91"/>
-      <c r="G13" s="92"/>
+      <c r="E13" s="91">
+        <v>1347412</v>
+      </c>
+      <c r="F13" s="92"/>
+      <c r="G13" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -3281,262 +3316,411 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E32"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.8" outlineLevelCol="4"/>
+  <dimension ref="A1:D28"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.8" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10.5703125" style="12" customWidth="1"/>
     <col min="2" max="2" width="12.6015625" style="44" customWidth="1"/>
-    <col min="3" max="3" width="36.125" style="12" customWidth="1"/>
-    <col min="4" max="4" width="18.828125" style="12" customWidth="1"/>
-    <col min="5" max="5" width="12.2890625" style="12" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="12"/>
+    <col min="3" max="3" width="18.828125" style="12" customWidth="1"/>
+    <col min="4" max="4" width="12.2890625" style="45" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" s="43" customFormat="1" ht="19" customHeight="1" spans="1:5">
-      <c r="A1" s="45" t="s">
+    <row r="1" s="43" customFormat="1" ht="26" spans="1:4">
+      <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="45" t="s">
+      <c r="C1" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="48" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" s="12" customFormat="1" spans="1:4">
+      <c r="A2" s="49">
+        <v>46054</v>
+      </c>
+      <c r="B2" s="50">
+        <v>1490</v>
+      </c>
+      <c r="C2" s="51">
+        <f>64000</f>
+        <v>64000</v>
+      </c>
+      <c r="D2" s="52">
+        <f>C2/8000</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" s="12" customFormat="1" spans="1:4">
+      <c r="A3" s="49">
+        <v>46055</v>
+      </c>
+      <c r="B3" s="50">
+        <v>1491</v>
+      </c>
+      <c r="C3" s="53">
+        <v>48000</v>
+      </c>
+      <c r="D3" s="52">
+        <f t="shared" ref="D3:D25" si="0">C3/8000</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" s="12" customFormat="1" spans="1:4">
+      <c r="A4" s="49">
+        <v>46056</v>
+      </c>
+      <c r="B4" s="50">
+        <v>1492</v>
+      </c>
+      <c r="C4" s="53">
+        <v>24000</v>
+      </c>
+      <c r="D4" s="52">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" s="12" customFormat="1" spans="1:4">
+      <c r="A5" s="49">
+        <v>46057</v>
+      </c>
+      <c r="B5" s="50">
+        <v>1493</v>
+      </c>
+      <c r="C5" s="53">
+        <v>96000</v>
+      </c>
+      <c r="D5" s="52">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" s="12" customFormat="1" spans="1:4">
+      <c r="A6" s="49">
+        <v>46058</v>
+      </c>
+      <c r="B6" s="50">
+        <v>1494</v>
+      </c>
+      <c r="C6" s="53">
+        <v>8000</v>
+      </c>
+      <c r="D6" s="52">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" s="12" customFormat="1" spans="1:4">
+      <c r="A7" s="49">
+        <v>46060</v>
+      </c>
+      <c r="B7" s="50">
+        <v>1495</v>
+      </c>
+      <c r="C7" s="53">
+        <v>40000</v>
+      </c>
+      <c r="D7" s="52">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" s="12" customFormat="1" spans="1:4">
+      <c r="A8" s="49">
+        <v>46061</v>
+      </c>
+      <c r="B8" s="50">
+        <v>1496</v>
+      </c>
+      <c r="C8" s="53">
+        <v>24000</v>
+      </c>
+      <c r="D8" s="52">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" s="12" customFormat="1" spans="1:4">
+      <c r="A9" s="49">
+        <v>46062</v>
+      </c>
+      <c r="B9" s="50">
+        <v>1497</v>
+      </c>
+      <c r="C9" s="53">
+        <v>48000</v>
+      </c>
+      <c r="D9" s="52">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" s="12" customFormat="1" spans="1:4">
+      <c r="A10" s="49">
+        <v>46063</v>
+      </c>
+      <c r="B10" s="50">
+        <v>1498</v>
+      </c>
+      <c r="C10" s="53">
+        <v>24000</v>
+      </c>
+      <c r="D10" s="52">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" s="12" customFormat="1" spans="1:4">
+      <c r="A11" s="49">
+        <v>46064</v>
+      </c>
+      <c r="B11" s="50">
+        <v>1499</v>
+      </c>
+      <c r="C11" s="53">
+        <v>32000</v>
+      </c>
+      <c r="D11" s="52">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="D1" s="45" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="45" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="2" s="12" customFormat="1" ht="263.65" customHeight="1" spans="1:5">
-      <c r="A2" s="47"/>
-      <c r="B2" s="48"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="49"/>
-    </row>
-    <row r="3" s="12" customFormat="1" ht="255.1" customHeight="1" spans="1:5">
-      <c r="A3" s="47"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="56"/>
-    </row>
-    <row r="4" s="12" customFormat="1" ht="249.95" customHeight="1" spans="1:5">
-      <c r="A4" s="47"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="56"/>
-    </row>
-    <row r="5" s="12" customFormat="1" ht="256.25" customHeight="1" spans="1:5">
-      <c r="A5" s="47"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="56"/>
-    </row>
-    <row r="6" s="12" customFormat="1" ht="253.85" customHeight="1" spans="1:5">
-      <c r="A6" s="47"/>
-      <c r="B6" s="48"/>
-      <c r="C6" s="49"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="56"/>
-    </row>
-    <row r="7" s="12" customFormat="1" ht="254.65" customHeight="1" spans="1:5">
-      <c r="A7" s="47"/>
-      <c r="B7" s="48"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="51"/>
-      <c r="E7" s="56"/>
-    </row>
-    <row r="8" s="12" customFormat="1" ht="255.35" customHeight="1" spans="1:5">
-      <c r="A8" s="47"/>
-      <c r="B8" s="48"/>
-      <c r="C8" s="49"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="56"/>
-    </row>
-    <row r="9" s="12" customFormat="1" ht="266.95" customHeight="1" spans="1:5">
-      <c r="A9" s="47"/>
-      <c r="B9" s="48"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="56"/>
-    </row>
-    <row r="10" s="12" customFormat="1" ht="261.95" customHeight="1" spans="1:5">
-      <c r="A10" s="47"/>
-      <c r="B10" s="48"/>
-      <c r="C10" s="49"/>
-      <c r="D10" s="51"/>
-      <c r="E10" s="56"/>
-    </row>
-    <row r="11" s="12" customFormat="1" ht="261.9" customHeight="1" spans="1:5">
-      <c r="A11" s="47"/>
-      <c r="B11" s="48"/>
-      <c r="C11" s="49"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="56"/>
-    </row>
-    <row r="12" s="12" customFormat="1" ht="270.7" customHeight="1" spans="1:5">
-      <c r="A12" s="47"/>
-      <c r="B12" s="48"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="51"/>
-      <c r="E12" s="56"/>
-    </row>
-    <row r="13" s="12" customFormat="1" ht="261.1" customHeight="1" spans="1:5">
-      <c r="A13" s="47"/>
-      <c r="B13" s="48"/>
-      <c r="C13" s="49"/>
-      <c r="D13" s="51"/>
-      <c r="E13" s="56"/>
-    </row>
-    <row r="14" s="12" customFormat="1" ht="257.15" customHeight="1" spans="1:5">
-      <c r="A14" s="47"/>
-      <c r="B14" s="48"/>
-      <c r="C14" s="49"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="56"/>
-    </row>
-    <row r="15" s="12" customFormat="1" ht="263.55" customHeight="1" spans="1:5">
-      <c r="A15" s="47"/>
-      <c r="B15" s="48"/>
-      <c r="C15" s="49"/>
-      <c r="D15" s="51"/>
-      <c r="E15" s="56"/>
-    </row>
-    <row r="16" s="12" customFormat="1" ht="270.35" customHeight="1" spans="1:5">
-      <c r="A16" s="47"/>
-      <c r="B16" s="48"/>
-      <c r="C16" s="49"/>
-      <c r="D16" s="51"/>
-      <c r="E16" s="56"/>
-    </row>
-    <row r="17" s="12" customFormat="1" ht="261.7" customHeight="1" spans="1:5">
-      <c r="A17" s="47"/>
-      <c r="B17" s="48"/>
-      <c r="C17" s="49"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="56"/>
-    </row>
-    <row r="18" s="12" customFormat="1" ht="260" customHeight="1" spans="1:5">
-      <c r="A18" s="47"/>
-      <c r="B18" s="48"/>
-      <c r="C18" s="49"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="56"/>
-    </row>
-    <row r="19" s="12" customFormat="1" ht="263.2" customHeight="1" spans="1:5">
-      <c r="A19" s="47"/>
-      <c r="B19" s="48"/>
-      <c r="C19" s="49"/>
-      <c r="D19" s="51"/>
-      <c r="E19" s="56"/>
-    </row>
-    <row r="20" s="12" customFormat="1" ht="289.95" customHeight="1" spans="1:5">
-      <c r="A20" s="47"/>
-      <c r="B20" s="48"/>
-      <c r="C20" s="49"/>
-      <c r="D20" s="51"/>
-      <c r="E20" s="56"/>
-    </row>
-    <row r="21" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A21" s="47"/>
-      <c r="B21" s="48"/>
-      <c r="C21" s="49"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="56"/>
-    </row>
-    <row r="22" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A22" s="47"/>
-      <c r="B22" s="48"/>
-      <c r="C22" s="49"/>
-      <c r="D22" s="51"/>
-      <c r="E22" s="56"/>
-    </row>
-    <row r="23" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A23" s="47"/>
-      <c r="B23" s="48"/>
-      <c r="C23" s="49"/>
-      <c r="D23" s="51"/>
-      <c r="E23" s="56"/>
-    </row>
-    <row r="24" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A24" s="47"/>
-      <c r="B24" s="48"/>
-      <c r="C24" s="49"/>
-      <c r="D24" s="50"/>
-      <c r="E24" s="49"/>
-    </row>
-    <row r="25" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A25" s="47"/>
-      <c r="B25" s="48"/>
-      <c r="C25" s="49"/>
-      <c r="D25" s="50"/>
-      <c r="E25" s="49"/>
-    </row>
-    <row r="26" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A26" s="47"/>
-      <c r="B26" s="48"/>
-      <c r="C26" s="49"/>
-      <c r="D26" s="50"/>
-      <c r="E26" s="49"/>
-    </row>
-    <row r="27" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A27" s="47">
-        <v>45960</v>
-      </c>
-      <c r="B27" s="48"/>
-      <c r="C27" s="49"/>
-      <c r="D27" s="50"/>
-      <c r="E27" s="49"/>
-    </row>
-    <row r="28" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A28" s="47">
-        <v>45961</v>
-      </c>
-      <c r="B28" s="48"/>
-      <c r="C28" s="49"/>
-      <c r="D28" s="50"/>
-      <c r="E28" s="49"/>
-    </row>
-    <row r="29" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A29" s="47"/>
-      <c r="B29" s="48"/>
-      <c r="C29" s="49"/>
-      <c r="D29" s="50"/>
-      <c r="E29" s="49"/>
-    </row>
-    <row r="30" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A30" s="47"/>
-      <c r="B30" s="48"/>
-      <c r="C30" s="49"/>
-      <c r="D30" s="50"/>
-      <c r="E30" s="49"/>
-    </row>
-    <row r="31" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A31" s="47"/>
-      <c r="B31" s="48"/>
-      <c r="C31" s="49"/>
-      <c r="D31" s="50"/>
-      <c r="E31" s="49"/>
-    </row>
-    <row r="32" s="12" customFormat="1" spans="1:5">
-      <c r="A32" s="52"/>
-      <c r="B32" s="53"/>
-      <c r="C32" s="54">
-        <f>SUM(D2:D31)</f>
+    </row>
+    <row r="12" s="12" customFormat="1" spans="1:4">
+      <c r="A12" s="49">
+        <v>46065</v>
+      </c>
+      <c r="B12" s="50">
+        <v>1500</v>
+      </c>
+      <c r="C12" s="53">
+        <v>40000</v>
+      </c>
+      <c r="D12" s="52">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" s="12" customFormat="1" spans="1:4">
+      <c r="A13" s="49">
+        <v>46066</v>
+      </c>
+      <c r="B13" s="162" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="53">
+        <v>48000</v>
+      </c>
+      <c r="D13" s="52">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" s="12" customFormat="1" spans="1:4">
+      <c r="A14" s="49">
+        <v>46067</v>
+      </c>
+      <c r="B14" s="162" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="53">
+        <v>40000</v>
+      </c>
+      <c r="D14" s="52">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" s="12" customFormat="1" spans="1:4">
+      <c r="A15" s="49">
+        <v>46068</v>
+      </c>
+      <c r="B15" s="162" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="53">
+        <v>40000</v>
+      </c>
+      <c r="D15" s="52">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" s="12" customFormat="1" spans="1:4">
+      <c r="A16" s="49">
+        <v>46069</v>
+      </c>
+      <c r="B16" s="162" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="53">
+        <v>40000</v>
+      </c>
+      <c r="D16" s="52">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" s="12" customFormat="1" spans="1:4">
+      <c r="A17" s="49">
+        <v>46070</v>
+      </c>
+      <c r="B17" s="162" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="53">
+        <v>32000</v>
+      </c>
+      <c r="D17" s="52">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" s="12" customFormat="1" spans="1:4">
+      <c r="A18" s="49">
+        <v>46072</v>
+      </c>
+      <c r="B18" s="162" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="53">
+        <v>88000</v>
+      </c>
+      <c r="D18" s="52">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" s="12" customFormat="1" spans="1:4">
+      <c r="A19" s="49">
+        <v>46074</v>
+      </c>
+      <c r="B19" s="162" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="53">
+        <v>24000</v>
+      </c>
+      <c r="D19" s="52">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" s="12" customFormat="1" spans="1:4">
+      <c r="A20" s="49">
+        <v>46076</v>
+      </c>
+      <c r="B20" s="162" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="51">
+        <v>110000</v>
+      </c>
+      <c r="D20" s="52">
+        <f t="shared" si="0"/>
+        <v>13.75</v>
+      </c>
+    </row>
+    <row r="21" s="12" customFormat="1" spans="1:4">
+      <c r="A21" s="49">
+        <v>46077</v>
+      </c>
+      <c r="B21" s="162" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="51">
+        <v>48000</v>
+      </c>
+      <c r="D21" s="52">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" s="12" customFormat="1" spans="1:4">
+      <c r="A22" s="49">
+        <v>46078</v>
+      </c>
+      <c r="B22" s="162" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="51">
+        <v>32000</v>
+      </c>
+      <c r="D22" s="52">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" s="12" customFormat="1" spans="1:4">
+      <c r="A23" s="49">
+        <v>46079</v>
+      </c>
+      <c r="B23" s="162" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="51">
+        <v>96000</v>
+      </c>
+      <c r="D23" s="52">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" s="12" customFormat="1" spans="1:4">
+      <c r="A24" s="49">
+        <v>46080</v>
+      </c>
+      <c r="B24" s="162" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" s="51">
+        <v>32000</v>
+      </c>
+      <c r="D24" s="52">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" s="12" customFormat="1" spans="1:4">
+      <c r="A25" s="49">
+        <v>46081</v>
+      </c>
+      <c r="B25" s="50"/>
+      <c r="C25" s="51"/>
+      <c r="D25" s="52">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D32" s="55"/>
-      <c r="E32" s="57"/>
+    </row>
+    <row r="26" s="12" customFormat="1" ht="200" customHeight="1" spans="1:4">
+      <c r="A26" s="49"/>
+      <c r="B26" s="50"/>
+      <c r="C26" s="51"/>
+      <c r="D26" s="52"/>
+    </row>
+    <row r="27" s="12" customFormat="1" ht="200" customHeight="1" spans="1:4">
+      <c r="A27" s="49"/>
+      <c r="B27" s="50"/>
+      <c r="C27" s="51"/>
+      <c r="D27" s="52"/>
+    </row>
+    <row r="28" s="12" customFormat="1" spans="1:4">
+      <c r="A28" s="54"/>
+      <c r="B28" s="55"/>
+      <c r="C28" s="56"/>
+      <c r="D28" s="57">
+        <f>SUM(C:C)</f>
+        <v>1078000</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:E32"/>
+  <mergeCells count="1">
+    <mergeCell ref="A28:B28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -3562,10 +3746,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D1" s="17" t="s">
         <v>4</v>
@@ -3585,7 +3769,7 @@
         <v>46056</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="C2" s="20">
         <v>5</v>
@@ -3608,7 +3792,7 @@
         <v>46069</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="C3" s="24">
         <v>10</v>
@@ -3629,7 +3813,7 @@
     <row r="4" s="12" customFormat="1" ht="150" customHeight="1" spans="1:7">
       <c r="A4" s="26"/>
       <c r="B4" s="27" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="C4" s="24">
         <v>5</v>
@@ -3701,13 +3885,13 @@
   <sheetData>
     <row r="1" ht="25" customHeight="1" spans="1:3">
       <c r="A1" s="3" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3715,7 +3899,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="C2" s="8">
         <f>'Anugrah (Bag, Cup, Box)'!H12</f>
@@ -3727,7 +3911,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C3" s="8">
         <f>'UD Abdi Jaya (Bag, Cup, Box)'!H19</f>
@@ -3739,11 +3923,11 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="C4" s="8">
         <f>'PT. SUPARMA JAYA TBK (Tissue)'!E13</f>
-        <v>1347412.62304</v>
+        <v>1347412</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3751,11 +3935,11 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C5" s="9">
-        <f>'Vickel Laundry'!C32</f>
-        <v>0</v>
+        <f>'Vickel Laundry'!D28</f>
+        <v>1078000</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3763,7 +3947,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C6" s="9">
         <f>'Dishy Soap'!G7</f>
@@ -3777,7 +3961,7 @@
       <c r="B7" s="7"/>
       <c r="C7" s="10">
         <f>SUM(C2:C5)</f>
-        <v>14713912.62304</v>
+        <v>15791912</v>
       </c>
     </row>
   </sheetData>
